--- a/Test/TestPlan_MeowScanner.xlsx
+++ b/Test/TestPlan_MeowScanner.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Choedtrakun\MeowScannerWebForTest\Test\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AEE96D39-B638-4255-9C02-65F06EC3FE91}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ADC83DFA-2257-4EDA-865C-230D7BAF8FCC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="799" uniqueCount="514">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="858" uniqueCount="517">
   <si>
     <t>Test case Design and Results</t>
   </si>
@@ -1575,6 +1575,15 @@
   </si>
   <si>
     <t>แสดง "Welcome, {user.name}" ตรงกับ user ที่ login</t>
+  </si>
+  <si>
+    <t>Welcome, {name} ตรงกับ user ที่ login</t>
+  </si>
+  <si>
+    <t>Welcome, {name}</t>
+  </si>
+  <si>
+    <t>TC-M03</t>
   </si>
 </sst>
 </file>
@@ -1606,7 +1615,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1637,6 +1646,18 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF00B050"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF339933"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF0000"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1813,7 +1834,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="77">
+  <cellXfs count="91">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1869,6 +1890,36 @@
     <xf numFmtId="0" fontId="3" fillId="6" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="6" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="6" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1929,8 +1980,8 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1940,6 +1991,18 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -1974,15 +2037,6 @@
     <xf numFmtId="0" fontId="1" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -1995,11 +2049,20 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -2007,12 +2070,12 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -2025,6 +2088,11 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <mruColors>
+      <color rgb="FF339933"/>
+    </mruColors>
+  </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -2321,7 +2389,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A4:K123"/>
+  <dimension ref="A4:K124"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
@@ -2353,15 +2421,15 @@
       <c r="K4" s="14"/>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A5" s="68" t="s">
+      <c r="A5" s="79" t="s">
         <v>1</v>
       </c>
-      <c r="B5" s="47"/>
-      <c r="C5" s="46" t="s">
+      <c r="B5" s="57"/>
+      <c r="C5" s="56" t="s">
         <v>2</v>
       </c>
-      <c r="D5" s="47"/>
-      <c r="E5" s="47"/>
+      <c r="D5" s="57"/>
+      <c r="E5" s="57"/>
       <c r="F5" s="14"/>
       <c r="G5" s="14"/>
       <c r="H5" s="14"/>
@@ -2370,15 +2438,15 @@
       <c r="K5" s="14"/>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A6" s="68" t="s">
+      <c r="A6" s="79" t="s">
         <v>3</v>
       </c>
-      <c r="B6" s="47"/>
-      <c r="C6" s="46" t="s">
+      <c r="B6" s="57"/>
+      <c r="C6" s="56" t="s">
         <v>4</v>
       </c>
-      <c r="D6" s="47"/>
-      <c r="E6" s="47"/>
+      <c r="D6" s="57"/>
+      <c r="E6" s="57"/>
       <c r="F6" s="14"/>
       <c r="G6" s="14"/>
       <c r="H6" s="14"/>
@@ -2391,11 +2459,11 @@
         <v>5</v>
       </c>
       <c r="B7" s="61"/>
-      <c r="C7" s="69" t="s">
+      <c r="C7" s="83" t="s">
         <v>6</v>
       </c>
-      <c r="D7" s="47"/>
-      <c r="E7" s="47"/>
+      <c r="D7" s="57"/>
+      <c r="E7" s="57"/>
       <c r="F7" s="60" t="s">
         <v>7</v>
       </c>
@@ -2429,404 +2497,422 @@
       <c r="K8" s="62"/>
     </row>
     <row r="9" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="54" t="s">
+      <c r="A9" s="68" t="s">
         <v>13</v>
       </c>
-      <c r="B9" s="67"/>
+      <c r="B9" s="80"/>
       <c r="C9" s="15" t="s">
         <v>14</v>
       </c>
       <c r="D9" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="E9" s="58" t="s">
+      <c r="E9" s="72" t="s">
         <v>16</v>
       </c>
-      <c r="F9" s="54" t="s">
+      <c r="F9" s="68" t="s">
         <v>17</v>
       </c>
-      <c r="G9" s="55"/>
-      <c r="H9" s="50"/>
-      <c r="I9" s="51"/>
-      <c r="J9" s="50"/>
-      <c r="K9" s="51"/>
+      <c r="G9" s="69"/>
+      <c r="H9" s="64"/>
+      <c r="I9" s="65"/>
+      <c r="J9" s="29" t="s">
+        <v>298</v>
+      </c>
+      <c r="K9" s="30"/>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A10" s="56"/>
-      <c r="B10" s="70"/>
+      <c r="A10" s="70"/>
+      <c r="B10" s="84"/>
       <c r="C10" s="16" t="s">
         <v>18</v>
       </c>
       <c r="D10" s="11" t="s">
         <v>19</v>
       </c>
-      <c r="E10" s="59"/>
-      <c r="F10" s="56"/>
-      <c r="G10" s="57"/>
-      <c r="H10" s="52"/>
-      <c r="I10" s="53"/>
-      <c r="J10" s="52"/>
-      <c r="K10" s="53"/>
+      <c r="E10" s="73"/>
+      <c r="F10" s="70"/>
+      <c r="G10" s="71"/>
+      <c r="H10" s="66"/>
+      <c r="I10" s="67"/>
+      <c r="J10" s="33"/>
+      <c r="K10" s="34"/>
     </row>
     <row r="11" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="31" t="s">
+      <c r="A11" s="41" t="s">
         <v>20</v>
       </c>
-      <c r="B11" s="32"/>
+      <c r="B11" s="42"/>
       <c r="C11" s="17" t="s">
         <v>14</v>
       </c>
       <c r="D11" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="E11" s="37" t="s">
+      <c r="E11" s="47" t="s">
         <v>16</v>
       </c>
-      <c r="F11" s="31" t="s">
+      <c r="F11" s="41" t="s">
         <v>21</v>
       </c>
-      <c r="G11" s="32"/>
-      <c r="H11" s="25"/>
-      <c r="I11" s="26"/>
-      <c r="J11" s="25"/>
-      <c r="K11" s="26"/>
+      <c r="G11" s="42"/>
+      <c r="H11" s="35"/>
+      <c r="I11" s="36"/>
+      <c r="J11" s="29" t="s">
+        <v>298</v>
+      </c>
+      <c r="K11" s="30"/>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A12" s="35"/>
-      <c r="B12" s="36"/>
+      <c r="A12" s="45"/>
+      <c r="B12" s="46"/>
       <c r="C12" s="18" t="s">
         <v>18</v>
       </c>
       <c r="D12" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="E12" s="39"/>
-      <c r="F12" s="35"/>
-      <c r="G12" s="36"/>
-      <c r="H12" s="29"/>
-      <c r="I12" s="30"/>
-      <c r="J12" s="29"/>
-      <c r="K12" s="30"/>
+      <c r="E12" s="49"/>
+      <c r="F12" s="45"/>
+      <c r="G12" s="46"/>
+      <c r="H12" s="39"/>
+      <c r="I12" s="40"/>
+      <c r="J12" s="33"/>
+      <c r="K12" s="34"/>
     </row>
     <row r="13" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="31" t="s">
+      <c r="A13" s="41" t="s">
         <v>23</v>
       </c>
-      <c r="B13" s="32"/>
+      <c r="B13" s="42"/>
       <c r="C13" s="18" t="s">
         <v>14</v>
       </c>
       <c r="D13" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="E13" s="37" t="s">
+      <c r="E13" s="47" t="s">
         <v>16</v>
       </c>
-      <c r="F13" s="31" t="s">
+      <c r="F13" s="41" t="s">
         <v>21</v>
       </c>
-      <c r="G13" s="32"/>
-      <c r="H13" s="25"/>
-      <c r="I13" s="26"/>
-      <c r="J13" s="25"/>
-      <c r="K13" s="26"/>
+      <c r="G13" s="42"/>
+      <c r="H13" s="35"/>
+      <c r="I13" s="36"/>
+      <c r="J13" s="29" t="s">
+        <v>298</v>
+      </c>
+      <c r="K13" s="30"/>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A14" s="35"/>
-      <c r="B14" s="36"/>
+      <c r="A14" s="45"/>
+      <c r="B14" s="46"/>
       <c r="C14" s="18" t="s">
         <v>18</v>
       </c>
       <c r="D14" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="E14" s="39"/>
-      <c r="F14" s="35"/>
-      <c r="G14" s="36"/>
-      <c r="H14" s="29"/>
-      <c r="I14" s="30"/>
-      <c r="J14" s="29"/>
-      <c r="K14" s="30"/>
+      <c r="E14" s="49"/>
+      <c r="F14" s="45"/>
+      <c r="G14" s="46"/>
+      <c r="H14" s="39"/>
+      <c r="I14" s="40"/>
+      <c r="J14" s="33"/>
+      <c r="K14" s="34"/>
     </row>
     <row r="15" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="31" t="s">
+      <c r="A15" s="41" t="s">
         <v>25</v>
       </c>
-      <c r="B15" s="32"/>
+      <c r="B15" s="42"/>
       <c r="C15" s="18" t="s">
         <v>14</v>
       </c>
       <c r="D15" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="E15" s="37" t="s">
+      <c r="E15" s="47" t="s">
         <v>16</v>
       </c>
-      <c r="F15" s="31" t="s">
+      <c r="F15" s="41" t="s">
         <v>21</v>
       </c>
-      <c r="G15" s="32"/>
-      <c r="H15" s="25"/>
-      <c r="I15" s="26"/>
-      <c r="J15" s="25"/>
-      <c r="K15" s="26"/>
+      <c r="G15" s="42"/>
+      <c r="H15" s="35"/>
+      <c r="I15" s="36"/>
+      <c r="J15" s="29" t="s">
+        <v>298</v>
+      </c>
+      <c r="K15" s="30"/>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A16" s="35"/>
-      <c r="B16" s="36"/>
+      <c r="A16" s="45"/>
+      <c r="B16" s="46"/>
       <c r="C16" s="18" t="s">
         <v>18</v>
       </c>
       <c r="D16" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="E16" s="39"/>
-      <c r="F16" s="35"/>
-      <c r="G16" s="36"/>
-      <c r="H16" s="29"/>
-      <c r="I16" s="30"/>
-      <c r="J16" s="29"/>
-      <c r="K16" s="30"/>
+      <c r="E16" s="49"/>
+      <c r="F16" s="45"/>
+      <c r="G16" s="46"/>
+      <c r="H16" s="39"/>
+      <c r="I16" s="40"/>
+      <c r="J16" s="33"/>
+      <c r="K16" s="34"/>
     </row>
     <row r="17" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="31" t="s">
+      <c r="A17" s="41" t="s">
         <v>26</v>
       </c>
-      <c r="B17" s="32"/>
+      <c r="B17" s="42"/>
       <c r="C17" s="18" t="s">
         <v>14</v>
       </c>
       <c r="D17" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="E17" s="37" t="s">
+      <c r="E17" s="47" t="s">
         <v>16</v>
       </c>
-      <c r="F17" s="31" t="s">
+      <c r="F17" s="41" t="s">
         <v>28</v>
       </c>
-      <c r="G17" s="32"/>
-      <c r="H17" s="25"/>
-      <c r="I17" s="26"/>
-      <c r="J17" s="25"/>
-      <c r="K17" s="26"/>
+      <c r="G17" s="42"/>
+      <c r="H17" s="35"/>
+      <c r="I17" s="36"/>
+      <c r="J17" s="29" t="s">
+        <v>298</v>
+      </c>
+      <c r="K17" s="30"/>
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A18" s="35"/>
-      <c r="B18" s="36"/>
+      <c r="A18" s="45"/>
+      <c r="B18" s="46"/>
       <c r="C18" s="18" t="s">
         <v>18</v>
       </c>
       <c r="D18" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="E18" s="39"/>
-      <c r="F18" s="35"/>
-      <c r="G18" s="36"/>
-      <c r="H18" s="29"/>
-      <c r="I18" s="30"/>
-      <c r="J18" s="29"/>
-      <c r="K18" s="30"/>
+      <c r="E18" s="49"/>
+      <c r="F18" s="45"/>
+      <c r="G18" s="46"/>
+      <c r="H18" s="39"/>
+      <c r="I18" s="40"/>
+      <c r="J18" s="33"/>
+      <c r="K18" s="34"/>
     </row>
     <row r="19" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="31" t="s">
+      <c r="A19" s="41" t="s">
         <v>29</v>
       </c>
-      <c r="B19" s="32"/>
+      <c r="B19" s="42"/>
       <c r="C19" s="18" t="s">
         <v>14</v>
       </c>
       <c r="D19" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="E19" s="37" t="s">
+      <c r="E19" s="47" t="s">
         <v>16</v>
       </c>
-      <c r="F19" s="31" t="s">
+      <c r="F19" s="41" t="s">
         <v>28</v>
       </c>
-      <c r="G19" s="32"/>
-      <c r="H19" s="25"/>
-      <c r="I19" s="26"/>
-      <c r="J19" s="25"/>
-      <c r="K19" s="26"/>
+      <c r="G19" s="42"/>
+      <c r="H19" s="35"/>
+      <c r="I19" s="36"/>
+      <c r="J19" s="29" t="s">
+        <v>298</v>
+      </c>
+      <c r="K19" s="30"/>
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A20" s="35"/>
-      <c r="B20" s="36"/>
+      <c r="A20" s="45"/>
+      <c r="B20" s="46"/>
       <c r="C20" s="18" t="s">
         <v>18</v>
       </c>
       <c r="D20" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="E20" s="39"/>
-      <c r="F20" s="35"/>
-      <c r="G20" s="36"/>
-      <c r="H20" s="29"/>
-      <c r="I20" s="30"/>
-      <c r="J20" s="29"/>
-      <c r="K20" s="30"/>
+      <c r="E20" s="49"/>
+      <c r="F20" s="45"/>
+      <c r="G20" s="46"/>
+      <c r="H20" s="39"/>
+      <c r="I20" s="40"/>
+      <c r="J20" s="33"/>
+      <c r="K20" s="34"/>
     </row>
     <row r="21" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="31" t="s">
+      <c r="A21" s="41" t="s">
         <v>30</v>
       </c>
-      <c r="B21" s="32"/>
+      <c r="B21" s="42"/>
       <c r="C21" s="18" t="s">
         <v>14</v>
       </c>
       <c r="D21" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="E21" s="37" t="s">
+      <c r="E21" s="47" t="s">
         <v>16</v>
       </c>
-      <c r="F21" s="31" t="s">
+      <c r="F21" s="41" t="s">
         <v>28</v>
       </c>
-      <c r="G21" s="32"/>
-      <c r="H21" s="25"/>
-      <c r="I21" s="26"/>
-      <c r="J21" s="25"/>
-      <c r="K21" s="26"/>
+      <c r="G21" s="42"/>
+      <c r="H21" s="35"/>
+      <c r="I21" s="36"/>
+      <c r="J21" s="29" t="s">
+        <v>298</v>
+      </c>
+      <c r="K21" s="30"/>
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A22" s="35"/>
-      <c r="B22" s="36"/>
+      <c r="A22" s="45"/>
+      <c r="B22" s="46"/>
       <c r="C22" s="18" t="s">
         <v>18</v>
       </c>
       <c r="D22" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="E22" s="39"/>
-      <c r="F22" s="35"/>
-      <c r="G22" s="36"/>
-      <c r="H22" s="29"/>
-      <c r="I22" s="30"/>
-      <c r="J22" s="29"/>
-      <c r="K22" s="30"/>
+      <c r="E22" s="49"/>
+      <c r="F22" s="45"/>
+      <c r="G22" s="46"/>
+      <c r="H22" s="39"/>
+      <c r="I22" s="40"/>
+      <c r="J22" s="33"/>
+      <c r="K22" s="34"/>
     </row>
     <row r="23" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="31" t="s">
+      <c r="A23" s="41" t="s">
         <v>31</v>
       </c>
-      <c r="B23" s="32"/>
+      <c r="B23" s="42"/>
       <c r="C23" s="18" t="s">
         <v>14</v>
       </c>
       <c r="D23" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="E23" s="37" t="s">
+      <c r="E23" s="47" t="s">
         <v>16</v>
       </c>
-      <c r="F23" s="31" t="s">
+      <c r="F23" s="41" t="s">
         <v>32</v>
       </c>
-      <c r="G23" s="32"/>
-      <c r="H23" s="25"/>
-      <c r="I23" s="26"/>
-      <c r="J23" s="25"/>
-      <c r="K23" s="26"/>
+      <c r="G23" s="42"/>
+      <c r="H23" s="35"/>
+      <c r="I23" s="36"/>
+      <c r="J23" s="29" t="s">
+        <v>298</v>
+      </c>
+      <c r="K23" s="30"/>
     </row>
     <row r="24" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A24" s="33"/>
-      <c r="B24" s="34"/>
+      <c r="A24" s="43"/>
+      <c r="B24" s="44"/>
       <c r="C24" s="18" t="s">
         <v>18</v>
       </c>
       <c r="D24" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="E24" s="38"/>
-      <c r="F24" s="33"/>
-      <c r="G24" s="34"/>
-      <c r="H24" s="27"/>
-      <c r="I24" s="28"/>
-      <c r="J24" s="27"/>
-      <c r="K24" s="28"/>
+      <c r="E24" s="48"/>
+      <c r="F24" s="43"/>
+      <c r="G24" s="44"/>
+      <c r="H24" s="37"/>
+      <c r="I24" s="38"/>
+      <c r="J24" s="31"/>
+      <c r="K24" s="32"/>
     </row>
     <row r="25" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A25" s="35"/>
-      <c r="B25" s="36"/>
+      <c r="A25" s="45"/>
+      <c r="B25" s="46"/>
       <c r="C25" s="18" t="s">
         <v>33</v>
       </c>
       <c r="D25" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="E25" s="39"/>
-      <c r="F25" s="35"/>
-      <c r="G25" s="36"/>
-      <c r="H25" s="29"/>
-      <c r="I25" s="30"/>
-      <c r="J25" s="29"/>
-      <c r="K25" s="30"/>
+      <c r="E25" s="49"/>
+      <c r="F25" s="45"/>
+      <c r="G25" s="46"/>
+      <c r="H25" s="39"/>
+      <c r="I25" s="40"/>
+      <c r="J25" s="33"/>
+      <c r="K25" s="34"/>
     </row>
     <row r="26" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="31" t="s">
+      <c r="A26" s="41" t="s">
         <v>35</v>
       </c>
-      <c r="B26" s="32"/>
+      <c r="B26" s="42"/>
       <c r="C26" s="18" t="s">
         <v>14</v>
       </c>
       <c r="D26" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="E26" s="37" t="s">
+      <c r="E26" s="47" t="s">
         <v>16</v>
       </c>
-      <c r="F26" s="31" t="s">
+      <c r="F26" s="41" t="s">
         <v>36</v>
       </c>
-      <c r="G26" s="32"/>
-      <c r="H26" s="25"/>
-      <c r="I26" s="26"/>
-      <c r="J26" s="25"/>
-      <c r="K26" s="26"/>
+      <c r="G26" s="42"/>
+      <c r="H26" s="35"/>
+      <c r="I26" s="36"/>
+      <c r="J26" s="29" t="s">
+        <v>298</v>
+      </c>
+      <c r="K26" s="30"/>
     </row>
     <row r="27" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A27" s="33"/>
-      <c r="B27" s="34"/>
+      <c r="A27" s="43"/>
+      <c r="B27" s="44"/>
       <c r="C27" s="18" t="s">
         <v>18</v>
       </c>
       <c r="D27" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="E27" s="38"/>
-      <c r="F27" s="33"/>
-      <c r="G27" s="34"/>
-      <c r="H27" s="27"/>
-      <c r="I27" s="28"/>
-      <c r="J27" s="27"/>
-      <c r="K27" s="28"/>
+      <c r="E27" s="48"/>
+      <c r="F27" s="43"/>
+      <c r="G27" s="44"/>
+      <c r="H27" s="37"/>
+      <c r="I27" s="38"/>
+      <c r="J27" s="31"/>
+      <c r="K27" s="32"/>
     </row>
     <row r="28" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A28" s="35"/>
-      <c r="B28" s="36"/>
+      <c r="A28" s="45"/>
+      <c r="B28" s="46"/>
       <c r="C28" s="18" t="s">
         <v>33</v>
       </c>
       <c r="D28" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="E28" s="39"/>
-      <c r="F28" s="35"/>
-      <c r="G28" s="36"/>
-      <c r="H28" s="29"/>
-      <c r="I28" s="30"/>
-      <c r="J28" s="29"/>
-      <c r="K28" s="30"/>
+      <c r="E28" s="49"/>
+      <c r="F28" s="45"/>
+      <c r="G28" s="46"/>
+      <c r="H28" s="39"/>
+      <c r="I28" s="40"/>
+      <c r="J28" s="33"/>
+      <c r="K28" s="34"/>
     </row>
     <row r="29" spans="1:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="48" t="s">
+      <c r="A29" s="58" t="s">
         <v>38</v>
       </c>
-      <c r="B29" s="45"/>
+      <c r="B29" s="59"/>
       <c r="C29" s="18" t="s">
         <v>39</v>
       </c>
@@ -2836,107 +2922,111 @@
       <c r="E29" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="F29" s="49" t="s">
+      <c r="F29" s="63" t="s">
         <v>42</v>
       </c>
-      <c r="G29" s="45"/>
-      <c r="H29" s="45"/>
-      <c r="I29" s="45"/>
-      <c r="J29" s="45"/>
-      <c r="K29" s="45"/>
+      <c r="G29" s="59"/>
+      <c r="H29" s="59"/>
+      <c r="I29" s="59"/>
+      <c r="J29" s="55" t="s">
+        <v>298</v>
+      </c>
+      <c r="K29" s="55"/>
     </row>
     <row r="30" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="40"/>
-      <c r="B30" s="41"/>
-      <c r="C30" s="41"/>
-      <c r="D30" s="41"/>
-      <c r="E30" s="41"/>
-      <c r="F30" s="41"/>
-      <c r="G30" s="41"/>
-      <c r="H30" s="41"/>
-      <c r="I30" s="41"/>
-      <c r="J30" s="41"/>
-      <c r="K30" s="42"/>
+      <c r="A30" s="50"/>
+      <c r="B30" s="51"/>
+      <c r="C30" s="51"/>
+      <c r="D30" s="51"/>
+      <c r="E30" s="51"/>
+      <c r="F30" s="51"/>
+      <c r="G30" s="51"/>
+      <c r="H30" s="51"/>
+      <c r="I30" s="51"/>
+      <c r="J30" s="51"/>
+      <c r="K30" s="52"/>
     </row>
     <row r="31" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A31" s="31" t="s">
+      <c r="A31" s="41" t="s">
         <v>43</v>
       </c>
-      <c r="B31" s="32"/>
+      <c r="B31" s="42"/>
       <c r="C31" s="18" t="s">
         <v>44</v>
       </c>
       <c r="D31" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="E31" s="37" t="s">
+      <c r="E31" s="47" t="s">
         <v>46</v>
       </c>
-      <c r="F31" s="31" t="s">
+      <c r="F31" s="41" t="s">
         <v>47</v>
       </c>
-      <c r="G31" s="32"/>
-      <c r="H31" s="25"/>
-      <c r="I31" s="26"/>
-      <c r="J31" s="25"/>
-      <c r="K31" s="26"/>
+      <c r="G31" s="42"/>
+      <c r="H31" s="35"/>
+      <c r="I31" s="36"/>
+      <c r="J31" s="29" t="s">
+        <v>298</v>
+      </c>
+      <c r="K31" s="30"/>
     </row>
     <row r="32" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A32" s="33"/>
-      <c r="B32" s="34"/>
+      <c r="A32" s="43"/>
+      <c r="B32" s="44"/>
       <c r="C32" s="18" t="s">
         <v>14</v>
       </c>
       <c r="D32" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="E32" s="38"/>
-      <c r="F32" s="33"/>
-      <c r="G32" s="34"/>
-      <c r="H32" s="27"/>
-      <c r="I32" s="28"/>
-      <c r="J32" s="27"/>
-      <c r="K32" s="28"/>
+      <c r="E32" s="48"/>
+      <c r="F32" s="43"/>
+      <c r="G32" s="44"/>
+      <c r="H32" s="37"/>
+      <c r="I32" s="38"/>
+      <c r="J32" s="31"/>
+      <c r="K32" s="32"/>
     </row>
     <row r="33" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A33" s="33"/>
-      <c r="B33" s="34"/>
+      <c r="A33" s="43"/>
+      <c r="B33" s="44"/>
       <c r="C33" s="18" t="s">
         <v>18</v>
       </c>
       <c r="D33" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="E33" s="38"/>
-      <c r="F33" s="33"/>
-      <c r="G33" s="34"/>
-      <c r="H33" s="27"/>
-      <c r="I33" s="28"/>
-      <c r="J33" s="27"/>
-      <c r="K33" s="28"/>
+      <c r="E33" s="48"/>
+      <c r="F33" s="43"/>
+      <c r="G33" s="44"/>
+      <c r="H33" s="37"/>
+      <c r="I33" s="38"/>
+      <c r="J33" s="31"/>
+      <c r="K33" s="32"/>
     </row>
     <row r="34" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A34" s="35"/>
-      <c r="B34" s="36"/>
+      <c r="A34" s="45"/>
+      <c r="B34" s="46"/>
       <c r="C34" s="18" t="s">
         <v>50</v>
       </c>
       <c r="D34" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="E34" s="39"/>
-      <c r="F34" s="35"/>
-      <c r="G34" s="36"/>
-      <c r="H34" s="29"/>
-      <c r="I34" s="30"/>
-      <c r="J34" s="29"/>
-      <c r="K34" s="30"/>
+      <c r="E34" s="49"/>
+      <c r="F34" s="45"/>
+      <c r="G34" s="46"/>
+      <c r="H34" s="39"/>
+      <c r="I34" s="40"/>
+      <c r="J34" s="33"/>
+      <c r="K34" s="34"/>
     </row>
     <row r="35" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A35" s="48" t="s">
+      <c r="A35" s="58" t="s">
         <v>51</v>
       </c>
-      <c r="B35" s="45"/>
+      <c r="B35" s="59"/>
       <c r="C35" s="18" t="s">
         <v>18</v>
       </c>
@@ -2946,20 +3036,22 @@
       <c r="E35" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="F35" s="49" t="s">
+      <c r="F35" s="63" t="s">
         <v>53</v>
       </c>
-      <c r="G35" s="45"/>
-      <c r="H35" s="45"/>
-      <c r="I35" s="45"/>
-      <c r="J35" s="45"/>
-      <c r="K35" s="45"/>
+      <c r="G35" s="59"/>
+      <c r="H35" s="59"/>
+      <c r="I35" s="59"/>
+      <c r="J35" s="55" t="s">
+        <v>298</v>
+      </c>
+      <c r="K35" s="55"/>
     </row>
     <row r="36" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A36" s="48" t="s">
+      <c r="A36" s="58" t="s">
         <v>54</v>
       </c>
-      <c r="B36" s="45"/>
+      <c r="B36" s="59"/>
       <c r="C36" s="18" t="s">
         <v>18</v>
       </c>
@@ -2969,20 +3061,22 @@
       <c r="E36" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="F36" s="49" t="s">
+      <c r="F36" s="63" t="s">
         <v>55</v>
       </c>
-      <c r="G36" s="45"/>
-      <c r="H36" s="45"/>
-      <c r="I36" s="45"/>
-      <c r="J36" s="45"/>
-      <c r="K36" s="45"/>
+      <c r="G36" s="59"/>
+      <c r="H36" s="59"/>
+      <c r="I36" s="59"/>
+      <c r="J36" s="55" t="s">
+        <v>298</v>
+      </c>
+      <c r="K36" s="55"/>
     </row>
     <row r="37" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A37" s="48" t="s">
+      <c r="A37" s="58" t="s">
         <v>56</v>
       </c>
-      <c r="B37" s="45"/>
+      <c r="B37" s="59"/>
       <c r="C37" s="18" t="s">
         <v>18</v>
       </c>
@@ -2992,20 +3086,22 @@
       <c r="E37" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="F37" s="49" t="s">
+      <c r="F37" s="63" t="s">
         <v>58</v>
       </c>
-      <c r="G37" s="45"/>
-      <c r="H37" s="45"/>
-      <c r="I37" s="45"/>
-      <c r="J37" s="45"/>
-      <c r="K37" s="45"/>
+      <c r="G37" s="59"/>
+      <c r="H37" s="59"/>
+      <c r="I37" s="59"/>
+      <c r="J37" s="55" t="s">
+        <v>298</v>
+      </c>
+      <c r="K37" s="55"/>
     </row>
     <row r="38" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A38" s="48" t="s">
+      <c r="A38" s="58" t="s">
         <v>59</v>
       </c>
-      <c r="B38" s="45"/>
+      <c r="B38" s="59"/>
       <c r="C38" s="18" t="s">
         <v>18</v>
       </c>
@@ -3015,20 +3111,22 @@
       <c r="E38" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="F38" s="49" t="s">
+      <c r="F38" s="63" t="s">
         <v>61</v>
       </c>
-      <c r="G38" s="45"/>
-      <c r="H38" s="45"/>
-      <c r="I38" s="45"/>
-      <c r="J38" s="45"/>
-      <c r="K38" s="45"/>
+      <c r="G38" s="59"/>
+      <c r="H38" s="59"/>
+      <c r="I38" s="59"/>
+      <c r="J38" s="55" t="s">
+        <v>298</v>
+      </c>
+      <c r="K38" s="55"/>
     </row>
     <row r="39" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A39" s="48" t="s">
+      <c r="A39" s="58" t="s">
         <v>62</v>
       </c>
-      <c r="B39" s="45"/>
+      <c r="B39" s="59"/>
       <c r="C39" s="18" t="s">
         <v>18</v>
       </c>
@@ -3038,20 +3136,22 @@
       <c r="E39" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="F39" s="49" t="s">
+      <c r="F39" s="63" t="s">
         <v>64</v>
       </c>
-      <c r="G39" s="45"/>
-      <c r="H39" s="45"/>
-      <c r="I39" s="45"/>
-      <c r="J39" s="45"/>
-      <c r="K39" s="45"/>
+      <c r="G39" s="59"/>
+      <c r="H39" s="59"/>
+      <c r="I39" s="59"/>
+      <c r="J39" s="55" t="s">
+        <v>298</v>
+      </c>
+      <c r="K39" s="55"/>
     </row>
     <row r="40" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A40" s="48" t="s">
+      <c r="A40" s="58" t="s">
         <v>65</v>
       </c>
-      <c r="B40" s="45"/>
+      <c r="B40" s="59"/>
       <c r="C40" s="18" t="s">
         <v>18</v>
       </c>
@@ -3061,20 +3161,22 @@
       <c r="E40" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="F40" s="49" t="s">
+      <c r="F40" s="63" t="s">
         <v>67</v>
       </c>
-      <c r="G40" s="45"/>
-      <c r="H40" s="45"/>
-      <c r="I40" s="45"/>
-      <c r="J40" s="45"/>
-      <c r="K40" s="45"/>
+      <c r="G40" s="59"/>
+      <c r="H40" s="59"/>
+      <c r="I40" s="59"/>
+      <c r="J40" s="55" t="s">
+        <v>298</v>
+      </c>
+      <c r="K40" s="55"/>
     </row>
     <row r="41" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A41" s="48" t="s">
+      <c r="A41" s="58" t="s">
         <v>68</v>
       </c>
-      <c r="B41" s="45"/>
+      <c r="B41" s="59"/>
       <c r="C41" s="18" t="s">
         <v>18</v>
       </c>
@@ -3084,20 +3186,22 @@
       <c r="E41" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="F41" s="49" t="s">
+      <c r="F41" s="63" t="s">
         <v>70</v>
       </c>
-      <c r="G41" s="45"/>
-      <c r="H41" s="45"/>
-      <c r="I41" s="45"/>
-      <c r="J41" s="45"/>
-      <c r="K41" s="45"/>
+      <c r="G41" s="59"/>
+      <c r="H41" s="59"/>
+      <c r="I41" s="59"/>
+      <c r="J41" s="55" t="s">
+        <v>298</v>
+      </c>
+      <c r="K41" s="55"/>
     </row>
     <row r="42" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A42" s="48" t="s">
+      <c r="A42" s="58" t="s">
         <v>71</v>
       </c>
-      <c r="B42" s="45"/>
+      <c r="B42" s="59"/>
       <c r="C42" s="18" t="s">
         <v>18</v>
       </c>
@@ -3107,20 +3211,22 @@
       <c r="E42" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="F42" s="49" t="s">
+      <c r="F42" s="63" t="s">
         <v>73</v>
       </c>
-      <c r="G42" s="45"/>
-      <c r="H42" s="45"/>
-      <c r="I42" s="45"/>
-      <c r="J42" s="45"/>
-      <c r="K42" s="45"/>
+      <c r="G42" s="59"/>
+      <c r="H42" s="59"/>
+      <c r="I42" s="59"/>
+      <c r="J42" s="55" t="s">
+        <v>298</v>
+      </c>
+      <c r="K42" s="55"/>
     </row>
     <row r="43" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A43" s="48" t="s">
+      <c r="A43" s="58" t="s">
         <v>74</v>
       </c>
-      <c r="B43" s="45"/>
+      <c r="B43" s="59"/>
       <c r="C43" s="18" t="s">
         <v>18</v>
       </c>
@@ -3130,20 +3236,22 @@
       <c r="E43" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="F43" s="49" t="s">
+      <c r="F43" s="63" t="s">
         <v>73</v>
       </c>
-      <c r="G43" s="45"/>
-      <c r="H43" s="45"/>
-      <c r="I43" s="45"/>
-      <c r="J43" s="45"/>
-      <c r="K43" s="45"/>
+      <c r="G43" s="59"/>
+      <c r="H43" s="59"/>
+      <c r="I43" s="59"/>
+      <c r="J43" s="55" t="s">
+        <v>298</v>
+      </c>
+      <c r="K43" s="55"/>
     </row>
     <row r="44" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A44" s="48" t="s">
+      <c r="A44" s="58" t="s">
         <v>76</v>
       </c>
-      <c r="B44" s="45"/>
+      <c r="B44" s="59"/>
       <c r="C44" s="18" t="s">
         <v>18</v>
       </c>
@@ -3153,20 +3261,22 @@
       <c r="E44" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="F44" s="49" t="s">
+      <c r="F44" s="63" t="s">
         <v>73</v>
       </c>
-      <c r="G44" s="45"/>
-      <c r="H44" s="45"/>
-      <c r="I44" s="45"/>
-      <c r="J44" s="45"/>
-      <c r="K44" s="45"/>
+      <c r="G44" s="59"/>
+      <c r="H44" s="59"/>
+      <c r="I44" s="59"/>
+      <c r="J44" s="55" t="s">
+        <v>298</v>
+      </c>
+      <c r="K44" s="55"/>
     </row>
     <row r="45" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="48" t="s">
+      <c r="A45" s="58" t="s">
         <v>78</v>
       </c>
-      <c r="B45" s="45"/>
+      <c r="B45" s="59"/>
       <c r="C45" s="18" t="s">
         <v>18</v>
       </c>
@@ -3176,60 +3286,64 @@
       <c r="E45" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="F45" s="49" t="s">
+      <c r="F45" s="63" t="s">
         <v>73</v>
       </c>
-      <c r="G45" s="45"/>
-      <c r="H45" s="45"/>
-      <c r="I45" s="45"/>
-      <c r="J45" s="45"/>
-      <c r="K45" s="45"/>
+      <c r="G45" s="59"/>
+      <c r="H45" s="59"/>
+      <c r="I45" s="59"/>
+      <c r="J45" s="55" t="s">
+        <v>298</v>
+      </c>
+      <c r="K45" s="55"/>
     </row>
     <row r="46" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A46" s="31" t="s">
+      <c r="A46" s="41" t="s">
         <v>80</v>
       </c>
-      <c r="B46" s="32"/>
+      <c r="B46" s="42"/>
       <c r="C46" s="18" t="s">
         <v>18</v>
       </c>
       <c r="D46" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="E46" s="37" t="s">
+      <c r="E46" s="47" t="s">
         <v>46</v>
       </c>
-      <c r="F46" s="31" t="s">
+      <c r="F46" s="41" t="s">
         <v>81</v>
       </c>
-      <c r="G46" s="32"/>
-      <c r="H46" s="25"/>
-      <c r="I46" s="26"/>
-      <c r="J46" s="25"/>
-      <c r="K46" s="26"/>
+      <c r="G46" s="42"/>
+      <c r="H46" s="35"/>
+      <c r="I46" s="36"/>
+      <c r="J46" s="29" t="s">
+        <v>298</v>
+      </c>
+      <c r="K46" s="30"/>
     </row>
     <row r="47" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A47" s="35"/>
-      <c r="B47" s="36"/>
+      <c r="A47" s="45"/>
+      <c r="B47" s="46"/>
       <c r="C47" s="18" t="s">
         <v>50</v>
       </c>
       <c r="D47" s="2" t="s">
         <v>82</v>
       </c>
-      <c r="E47" s="39"/>
-      <c r="F47" s="35"/>
-      <c r="G47" s="36"/>
-      <c r="H47" s="29"/>
-      <c r="I47" s="30"/>
-      <c r="J47" s="29"/>
-      <c r="K47" s="30"/>
+      <c r="E47" s="49"/>
+      <c r="F47" s="45"/>
+      <c r="G47" s="46"/>
+      <c r="H47" s="39"/>
+      <c r="I47" s="40"/>
+      <c r="J47" s="33"/>
+      <c r="K47" s="34"/>
     </row>
     <row r="48" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A48" s="48" t="s">
+      <c r="A48" s="58" t="s">
         <v>83</v>
       </c>
-      <c r="B48" s="45"/>
+      <c r="B48" s="59"/>
       <c r="C48" s="18" t="s">
         <v>44</v>
       </c>
@@ -3239,20 +3353,22 @@
       <c r="E48" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="F48" s="49" t="s">
+      <c r="F48" s="63" t="s">
         <v>84</v>
       </c>
-      <c r="G48" s="45"/>
-      <c r="H48" s="45"/>
-      <c r="I48" s="45"/>
-      <c r="J48" s="45"/>
-      <c r="K48" s="45"/>
+      <c r="G48" s="59"/>
+      <c r="H48" s="59"/>
+      <c r="I48" s="59"/>
+      <c r="J48" s="55" t="s">
+        <v>298</v>
+      </c>
+      <c r="K48" s="55"/>
     </row>
     <row r="49" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A49" s="48" t="s">
+      <c r="A49" s="58" t="s">
         <v>85</v>
       </c>
-      <c r="B49" s="45"/>
+      <c r="B49" s="59"/>
       <c r="C49" s="18" t="s">
         <v>14</v>
       </c>
@@ -3262,60 +3378,64 @@
       <c r="E49" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="F49" s="49" t="s">
+      <c r="F49" s="63" t="s">
         <v>84</v>
       </c>
-      <c r="G49" s="45"/>
-      <c r="H49" s="45"/>
-      <c r="I49" s="45"/>
-      <c r="J49" s="45"/>
-      <c r="K49" s="45"/>
+      <c r="G49" s="59"/>
+      <c r="H49" s="59"/>
+      <c r="I49" s="59"/>
+      <c r="J49" s="55" t="s">
+        <v>298</v>
+      </c>
+      <c r="K49" s="55"/>
     </row>
     <row r="50" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A50" s="31" t="s">
+      <c r="A50" s="41" t="s">
         <v>86</v>
       </c>
-      <c r="B50" s="32"/>
+      <c r="B50" s="42"/>
       <c r="C50" s="18" t="s">
         <v>14</v>
       </c>
       <c r="D50" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="E50" s="37" t="s">
+      <c r="E50" s="47" t="s">
         <v>46</v>
       </c>
-      <c r="F50" s="31" t="s">
+      <c r="F50" s="41" t="s">
         <v>87</v>
       </c>
-      <c r="G50" s="32"/>
-      <c r="H50" s="25"/>
-      <c r="I50" s="26"/>
-      <c r="J50" s="25"/>
-      <c r="K50" s="26"/>
+      <c r="G50" s="42"/>
+      <c r="H50" s="35"/>
+      <c r="I50" s="36"/>
+      <c r="J50" s="29" t="s">
+        <v>298</v>
+      </c>
+      <c r="K50" s="30"/>
     </row>
     <row r="51" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A51" s="35"/>
-      <c r="B51" s="36"/>
+      <c r="A51" s="45"/>
+      <c r="B51" s="46"/>
       <c r="C51" s="18" t="s">
         <v>18</v>
       </c>
       <c r="D51" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="E51" s="39"/>
-      <c r="F51" s="35"/>
-      <c r="G51" s="36"/>
-      <c r="H51" s="29"/>
-      <c r="I51" s="30"/>
-      <c r="J51" s="29"/>
-      <c r="K51" s="30"/>
+      <c r="E51" s="49"/>
+      <c r="F51" s="45"/>
+      <c r="G51" s="46"/>
+      <c r="H51" s="39"/>
+      <c r="I51" s="40"/>
+      <c r="J51" s="33"/>
+      <c r="K51" s="34"/>
     </row>
     <row r="52" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A52" s="48" t="s">
+      <c r="A52" s="58" t="s">
         <v>88</v>
       </c>
-      <c r="B52" s="45"/>
+      <c r="B52" s="59"/>
       <c r="C52" s="18" t="s">
         <v>39</v>
       </c>
@@ -3325,33 +3445,35 @@
       <c r="E52" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="F52" s="49" t="s">
+      <c r="F52" s="63" t="s">
         <v>42</v>
       </c>
-      <c r="G52" s="45"/>
-      <c r="H52" s="45"/>
-      <c r="I52" s="45"/>
-      <c r="J52" s="45"/>
-      <c r="K52" s="45"/>
+      <c r="G52" s="59"/>
+      <c r="H52" s="59"/>
+      <c r="I52" s="59"/>
+      <c r="J52" s="55" t="s">
+        <v>298</v>
+      </c>
+      <c r="K52" s="55"/>
     </row>
     <row r="53" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A53" s="40"/>
-      <c r="B53" s="41"/>
-      <c r="C53" s="41"/>
-      <c r="D53" s="41"/>
-      <c r="E53" s="41"/>
-      <c r="F53" s="41"/>
-      <c r="G53" s="41"/>
-      <c r="H53" s="41"/>
-      <c r="I53" s="41"/>
-      <c r="J53" s="41"/>
-      <c r="K53" s="42"/>
+      <c r="A53" s="50"/>
+      <c r="B53" s="51"/>
+      <c r="C53" s="51"/>
+      <c r="D53" s="51"/>
+      <c r="E53" s="51"/>
+      <c r="F53" s="51"/>
+      <c r="G53" s="51"/>
+      <c r="H53" s="51"/>
+      <c r="I53" s="51"/>
+      <c r="J53" s="51"/>
+      <c r="K53" s="52"/>
     </row>
     <row r="54" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A54" s="48" t="s">
+      <c r="A54" s="58" t="s">
         <v>90</v>
       </c>
-      <c r="B54" s="45"/>
+      <c r="B54" s="59"/>
       <c r="C54" s="18" t="s">
         <v>91</v>
       </c>
@@ -3361,20 +3483,20 @@
       <c r="E54" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="F54" s="49" t="s">
+      <c r="F54" s="63" t="s">
         <v>94</v>
       </c>
-      <c r="G54" s="45"/>
-      <c r="H54" s="45"/>
-      <c r="I54" s="45"/>
-      <c r="J54" s="45"/>
-      <c r="K54" s="45"/>
+      <c r="G54" s="59"/>
+      <c r="H54" s="59"/>
+      <c r="I54" s="59"/>
+      <c r="J54" s="59"/>
+      <c r="K54" s="59"/>
     </row>
     <row r="55" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A55" s="48" t="s">
+      <c r="A55" s="58" t="s">
         <v>95</v>
       </c>
-      <c r="B55" s="45"/>
+      <c r="B55" s="59"/>
       <c r="C55" s="18" t="s">
         <v>91</v>
       </c>
@@ -3384,20 +3506,20 @@
       <c r="E55" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="F55" s="49" t="s">
+      <c r="F55" s="63" t="s">
         <v>97</v>
       </c>
-      <c r="G55" s="45"/>
-      <c r="H55" s="45"/>
-      <c r="I55" s="45"/>
-      <c r="J55" s="45"/>
-      <c r="K55" s="45"/>
+      <c r="G55" s="59"/>
+      <c r="H55" s="59"/>
+      <c r="I55" s="59"/>
+      <c r="J55" s="59"/>
+      <c r="K55" s="59"/>
     </row>
     <row r="56" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A56" s="48" t="s">
+      <c r="A56" s="58" t="s">
         <v>98</v>
       </c>
-      <c r="B56" s="45"/>
+      <c r="B56" s="59"/>
       <c r="C56" s="18" t="s">
         <v>91</v>
       </c>
@@ -3407,20 +3529,20 @@
       <c r="E56" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="F56" s="49" t="s">
+      <c r="F56" s="63" t="s">
         <v>100</v>
       </c>
-      <c r="G56" s="45"/>
-      <c r="H56" s="45"/>
-      <c r="I56" s="45"/>
-      <c r="J56" s="45"/>
-      <c r="K56" s="45"/>
+      <c r="G56" s="59"/>
+      <c r="H56" s="59"/>
+      <c r="I56" s="59"/>
+      <c r="J56" s="59"/>
+      <c r="K56" s="59"/>
     </row>
     <row r="57" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A57" s="48" t="s">
+      <c r="A57" s="58" t="s">
         <v>101</v>
       </c>
-      <c r="B57" s="45"/>
+      <c r="B57" s="59"/>
       <c r="C57" s="18" t="s">
         <v>102</v>
       </c>
@@ -3430,20 +3552,20 @@
       <c r="E57" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="F57" s="49" t="s">
+      <c r="F57" s="63" t="s">
         <v>105</v>
       </c>
-      <c r="G57" s="45"/>
-      <c r="H57" s="45"/>
-      <c r="I57" s="45"/>
-      <c r="J57" s="45"/>
-      <c r="K57" s="45"/>
+      <c r="G57" s="59"/>
+      <c r="H57" s="59"/>
+      <c r="I57" s="59"/>
+      <c r="J57" s="59"/>
+      <c r="K57" s="59"/>
     </row>
     <row r="58" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A58" s="48" t="s">
+      <c r="A58" s="58" t="s">
         <v>106</v>
       </c>
-      <c r="B58" s="45"/>
+      <c r="B58" s="59"/>
       <c r="C58" s="18" t="s">
         <v>102</v>
       </c>
@@ -3453,20 +3575,20 @@
       <c r="E58" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="F58" s="49" t="s">
+      <c r="F58" s="63" t="s">
         <v>108</v>
       </c>
-      <c r="G58" s="45"/>
-      <c r="H58" s="45"/>
-      <c r="I58" s="45"/>
-      <c r="J58" s="45"/>
-      <c r="K58" s="45"/>
+      <c r="G58" s="59"/>
+      <c r="H58" s="59"/>
+      <c r="I58" s="59"/>
+      <c r="J58" s="59"/>
+      <c r="K58" s="59"/>
     </row>
     <row r="59" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A59" s="48" t="s">
+      <c r="A59" s="58" t="s">
         <v>109</v>
       </c>
-      <c r="B59" s="45"/>
+      <c r="B59" s="59"/>
       <c r="C59" s="18" t="s">
         <v>102</v>
       </c>
@@ -3476,20 +3598,20 @@
       <c r="E59" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="F59" s="49" t="s">
+      <c r="F59" s="63" t="s">
         <v>111</v>
       </c>
-      <c r="G59" s="45"/>
-      <c r="H59" s="45"/>
-      <c r="I59" s="45"/>
-      <c r="J59" s="45"/>
-      <c r="K59" s="45"/>
+      <c r="G59" s="59"/>
+      <c r="H59" s="59"/>
+      <c r="I59" s="59"/>
+      <c r="J59" s="59"/>
+      <c r="K59" s="59"/>
     </row>
     <row r="60" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A60" s="48" t="s">
+      <c r="A60" s="58" t="s">
         <v>112</v>
       </c>
-      <c r="B60" s="45"/>
+      <c r="B60" s="59"/>
       <c r="C60" s="18" t="s">
         <v>91</v>
       </c>
@@ -3499,14 +3621,14 @@
       <c r="E60" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="F60" s="49" t="s">
+      <c r="F60" s="63" t="s">
         <v>114</v>
       </c>
-      <c r="G60" s="45"/>
-      <c r="H60" s="45"/>
-      <c r="I60" s="45"/>
-      <c r="J60" s="45"/>
-      <c r="K60" s="45"/>
+      <c r="G60" s="59"/>
+      <c r="H60" s="59"/>
+      <c r="I60" s="59"/>
+      <c r="J60" s="59"/>
+      <c r="K60" s="59"/>
     </row>
     <row r="61" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A61" s="19"/>
@@ -3522,181 +3644,187 @@
       <c r="K61" s="21"/>
     </row>
     <row r="62" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A62" s="31" t="s">
+      <c r="A62" s="41" t="s">
         <v>115</v>
       </c>
-      <c r="B62" s="32"/>
+      <c r="B62" s="42"/>
       <c r="C62" s="18" t="s">
         <v>116</v>
       </c>
       <c r="D62" s="2" t="s">
         <v>117</v>
       </c>
-      <c r="E62" s="37" t="s">
+      <c r="E62" s="47" t="s">
         <v>118</v>
       </c>
-      <c r="F62" s="31" t="s">
+      <c r="F62" s="41" t="s">
         <v>119</v>
       </c>
-      <c r="G62" s="32"/>
-      <c r="H62" s="25"/>
-      <c r="I62" s="26"/>
-      <c r="J62" s="25"/>
-      <c r="K62" s="26"/>
+      <c r="G62" s="42"/>
+      <c r="H62" s="35"/>
+      <c r="I62" s="36"/>
+      <c r="J62" s="29" t="s">
+        <v>298</v>
+      </c>
+      <c r="K62" s="30"/>
     </row>
     <row r="63" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A63" s="33"/>
-      <c r="B63" s="34"/>
+      <c r="A63" s="43"/>
+      <c r="B63" s="44"/>
       <c r="C63" s="18" t="s">
         <v>120</v>
       </c>
       <c r="D63" s="2" t="s">
         <v>121</v>
       </c>
-      <c r="E63" s="38"/>
-      <c r="F63" s="33"/>
-      <c r="G63" s="34"/>
-      <c r="H63" s="27"/>
-      <c r="I63" s="28"/>
-      <c r="J63" s="27"/>
-      <c r="K63" s="28"/>
+      <c r="E63" s="48"/>
+      <c r="F63" s="43"/>
+      <c r="G63" s="44"/>
+      <c r="H63" s="37"/>
+      <c r="I63" s="38"/>
+      <c r="J63" s="31"/>
+      <c r="K63" s="32"/>
     </row>
     <row r="64" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A64" s="35"/>
-      <c r="B64" s="36"/>
+      <c r="A64" s="45"/>
+      <c r="B64" s="46"/>
       <c r="C64" s="18" t="s">
         <v>122</v>
       </c>
       <c r="D64" s="2" t="s">
         <v>123</v>
       </c>
-      <c r="E64" s="39"/>
-      <c r="F64" s="35"/>
-      <c r="G64" s="36"/>
-      <c r="H64" s="29"/>
-      <c r="I64" s="30"/>
-      <c r="J64" s="29"/>
-      <c r="K64" s="30"/>
+      <c r="E64" s="49"/>
+      <c r="F64" s="45"/>
+      <c r="G64" s="46"/>
+      <c r="H64" s="39"/>
+      <c r="I64" s="40"/>
+      <c r="J64" s="33"/>
+      <c r="K64" s="34"/>
     </row>
     <row r="65" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A65" s="31" t="s">
+      <c r="A65" s="41" t="s">
         <v>124</v>
       </c>
-      <c r="B65" s="32"/>
+      <c r="B65" s="42"/>
       <c r="C65" s="18" t="s">
         <v>116</v>
       </c>
       <c r="D65" s="2" t="s">
         <v>125</v>
       </c>
-      <c r="E65" s="37" t="s">
+      <c r="E65" s="47" t="s">
         <v>118</v>
       </c>
-      <c r="F65" s="31" t="s">
+      <c r="F65" s="41" t="s">
         <v>126</v>
       </c>
-      <c r="G65" s="32"/>
-      <c r="H65" s="25"/>
-      <c r="I65" s="26"/>
-      <c r="J65" s="25"/>
-      <c r="K65" s="26"/>
+      <c r="G65" s="42"/>
+      <c r="H65" s="35"/>
+      <c r="I65" s="36"/>
+      <c r="J65" s="29" t="s">
+        <v>298</v>
+      </c>
+      <c r="K65" s="30"/>
     </row>
     <row r="66" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A66" s="33"/>
-      <c r="B66" s="34"/>
+      <c r="A66" s="43"/>
+      <c r="B66" s="44"/>
       <c r="C66" s="18" t="s">
         <v>120</v>
       </c>
       <c r="D66" s="2" t="s">
         <v>127</v>
       </c>
-      <c r="E66" s="38"/>
-      <c r="F66" s="33"/>
-      <c r="G66" s="34"/>
-      <c r="H66" s="27"/>
-      <c r="I66" s="28"/>
-      <c r="J66" s="27"/>
-      <c r="K66" s="28"/>
+      <c r="E66" s="48"/>
+      <c r="F66" s="43"/>
+      <c r="G66" s="44"/>
+      <c r="H66" s="37"/>
+      <c r="I66" s="38"/>
+      <c r="J66" s="31"/>
+      <c r="K66" s="32"/>
     </row>
     <row r="67" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A67" s="35"/>
-      <c r="B67" s="36"/>
+      <c r="A67" s="45"/>
+      <c r="B67" s="46"/>
       <c r="C67" s="18" t="s">
         <v>122</v>
       </c>
       <c r="D67" s="2" t="s">
         <v>128</v>
       </c>
-      <c r="E67" s="39"/>
-      <c r="F67" s="35"/>
-      <c r="G67" s="36"/>
-      <c r="H67" s="29"/>
-      <c r="I67" s="30"/>
-      <c r="J67" s="29"/>
-      <c r="K67" s="30"/>
+      <c r="E67" s="49"/>
+      <c r="F67" s="45"/>
+      <c r="G67" s="46"/>
+      <c r="H67" s="39"/>
+      <c r="I67" s="40"/>
+      <c r="J67" s="33"/>
+      <c r="K67" s="34"/>
     </row>
     <row r="68" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A68" s="31" t="s">
+      <c r="A68" s="41" t="s">
         <v>129</v>
       </c>
-      <c r="B68" s="32"/>
+      <c r="B68" s="42"/>
       <c r="C68" s="18" t="s">
         <v>116</v>
       </c>
       <c r="D68" s="2" t="s">
         <v>130</v>
       </c>
-      <c r="E68" s="37" t="s">
+      <c r="E68" s="47" t="s">
         <v>118</v>
       </c>
-      <c r="F68" s="31" t="s">
+      <c r="F68" s="41" t="s">
         <v>131</v>
       </c>
-      <c r="G68" s="32"/>
-      <c r="H68" s="25"/>
-      <c r="I68" s="26"/>
-      <c r="J68" s="25"/>
-      <c r="K68" s="26"/>
+      <c r="G68" s="42"/>
+      <c r="H68" s="35"/>
+      <c r="I68" s="36"/>
+      <c r="J68" s="29" t="s">
+        <v>298</v>
+      </c>
+      <c r="K68" s="30"/>
     </row>
     <row r="69" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A69" s="33"/>
-      <c r="B69" s="34"/>
+      <c r="A69" s="43"/>
+      <c r="B69" s="44"/>
       <c r="C69" s="18" t="s">
         <v>120</v>
       </c>
       <c r="D69" s="2" t="s">
         <v>132</v>
       </c>
-      <c r="E69" s="38"/>
-      <c r="F69" s="33"/>
-      <c r="G69" s="34"/>
-      <c r="H69" s="27"/>
-      <c r="I69" s="28"/>
-      <c r="J69" s="27"/>
-      <c r="K69" s="28"/>
+      <c r="E69" s="48"/>
+      <c r="F69" s="43"/>
+      <c r="G69" s="44"/>
+      <c r="H69" s="37"/>
+      <c r="I69" s="38"/>
+      <c r="J69" s="31"/>
+      <c r="K69" s="32"/>
     </row>
     <row r="70" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A70" s="35"/>
-      <c r="B70" s="36"/>
+      <c r="A70" s="45"/>
+      <c r="B70" s="46"/>
       <c r="C70" s="18" t="s">
         <v>122</v>
       </c>
       <c r="D70" s="2" t="s">
         <v>133</v>
       </c>
-      <c r="E70" s="39"/>
-      <c r="F70" s="35"/>
-      <c r="G70" s="36"/>
-      <c r="H70" s="29"/>
-      <c r="I70" s="30"/>
-      <c r="J70" s="29"/>
-      <c r="K70" s="30"/>
+      <c r="E70" s="49"/>
+      <c r="F70" s="45"/>
+      <c r="G70" s="46"/>
+      <c r="H70" s="39"/>
+      <c r="I70" s="40"/>
+      <c r="J70" s="33"/>
+      <c r="K70" s="34"/>
     </row>
     <row r="71" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A71" s="43" t="s">
+      <c r="A71" s="53" t="s">
         <v>134</v>
       </c>
-      <c r="B71" s="44"/>
+      <c r="B71" s="54"/>
       <c r="C71" s="18" t="s">
         <v>135</v>
       </c>
@@ -3706,77 +3834,81 @@
       <c r="E71" s="2" t="s">
         <v>118</v>
       </c>
-      <c r="F71" s="63" t="s">
+      <c r="F71" s="74" t="s">
         <v>137</v>
       </c>
-      <c r="G71" s="64"/>
-      <c r="H71" s="45"/>
-      <c r="I71" s="45"/>
-      <c r="J71" s="45"/>
-      <c r="K71" s="45"/>
+      <c r="G71" s="75"/>
+      <c r="H71" s="59"/>
+      <c r="I71" s="59"/>
+      <c r="J71" s="55" t="s">
+        <v>298</v>
+      </c>
+      <c r="K71" s="55"/>
     </row>
     <row r="72" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A72" s="31" t="s">
+      <c r="A72" s="41" t="s">
         <v>138</v>
       </c>
-      <c r="B72" s="32"/>
+      <c r="B72" s="42"/>
       <c r="C72" s="18" t="s">
         <v>116</v>
       </c>
       <c r="D72" s="2" t="s">
         <v>117</v>
       </c>
-      <c r="E72" s="37" t="s">
+      <c r="E72" s="47" t="s">
         <v>118</v>
       </c>
-      <c r="F72" s="31" t="s">
+      <c r="F72" s="41" t="s">
         <v>139</v>
       </c>
-      <c r="G72" s="32"/>
-      <c r="H72" s="25"/>
-      <c r="I72" s="26"/>
-      <c r="J72" s="25"/>
-      <c r="K72" s="26"/>
+      <c r="G72" s="42"/>
+      <c r="H72" s="35"/>
+      <c r="I72" s="36"/>
+      <c r="J72" s="29" t="s">
+        <v>298</v>
+      </c>
+      <c r="K72" s="30"/>
     </row>
     <row r="73" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A73" s="33"/>
-      <c r="B73" s="34"/>
+      <c r="A73" s="43"/>
+      <c r="B73" s="44"/>
       <c r="C73" s="18" t="s">
         <v>120</v>
       </c>
       <c r="D73" s="2" t="s">
         <v>99</v>
       </c>
-      <c r="E73" s="38"/>
-      <c r="F73" s="33"/>
-      <c r="G73" s="34"/>
-      <c r="H73" s="27"/>
-      <c r="I73" s="28"/>
-      <c r="J73" s="27"/>
-      <c r="K73" s="28"/>
+      <c r="E73" s="48"/>
+      <c r="F73" s="43"/>
+      <c r="G73" s="44"/>
+      <c r="H73" s="37"/>
+      <c r="I73" s="38"/>
+      <c r="J73" s="31"/>
+      <c r="K73" s="32"/>
     </row>
     <row r="74" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A74" s="35"/>
-      <c r="B74" s="36"/>
+      <c r="A74" s="45"/>
+      <c r="B74" s="46"/>
       <c r="C74" s="18" t="s">
         <v>122</v>
       </c>
       <c r="D74" s="2" t="s">
         <v>99</v>
       </c>
-      <c r="E74" s="39"/>
-      <c r="F74" s="35"/>
-      <c r="G74" s="36"/>
-      <c r="H74" s="29"/>
-      <c r="I74" s="30"/>
-      <c r="J74" s="29"/>
-      <c r="K74" s="30"/>
+      <c r="E74" s="49"/>
+      <c r="F74" s="45"/>
+      <c r="G74" s="46"/>
+      <c r="H74" s="39"/>
+      <c r="I74" s="40"/>
+      <c r="J74" s="33"/>
+      <c r="K74" s="34"/>
     </row>
     <row r="75" spans="1:11" ht="30" x14ac:dyDescent="0.25">
-      <c r="A75" s="43" t="s">
+      <c r="A75" s="53" t="s">
         <v>140</v>
       </c>
-      <c r="B75" s="44"/>
+      <c r="B75" s="54"/>
       <c r="C75" s="18" t="s">
         <v>141</v>
       </c>
@@ -3786,20 +3918,22 @@
       <c r="E75" s="2" t="s">
         <v>143</v>
       </c>
-      <c r="F75" s="63" t="s">
+      <c r="F75" s="74" t="s">
         <v>144</v>
       </c>
-      <c r="G75" s="64"/>
-      <c r="H75" s="45"/>
-      <c r="I75" s="45"/>
-      <c r="J75" s="45"/>
-      <c r="K75" s="45"/>
+      <c r="G75" s="75"/>
+      <c r="H75" s="59"/>
+      <c r="I75" s="59"/>
+      <c r="J75" s="55" t="s">
+        <v>298</v>
+      </c>
+      <c r="K75" s="55"/>
     </row>
     <row r="76" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A76" s="43" t="s">
+      <c r="A76" s="53" t="s">
         <v>145</v>
       </c>
-      <c r="B76" s="44"/>
+      <c r="B76" s="54"/>
       <c r="C76" s="18" t="s">
         <v>141</v>
       </c>
@@ -3809,14 +3943,16 @@
       <c r="E76" s="2" t="s">
         <v>143</v>
       </c>
-      <c r="F76" s="63" t="s">
+      <c r="F76" s="74" t="s">
         <v>147</v>
       </c>
-      <c r="G76" s="64"/>
-      <c r="H76" s="45"/>
-      <c r="I76" s="45"/>
-      <c r="J76" s="45"/>
-      <c r="K76" s="45"/>
+      <c r="G76" s="75"/>
+      <c r="H76" s="59"/>
+      <c r="I76" s="59"/>
+      <c r="J76" s="55" t="s">
+        <v>298</v>
+      </c>
+      <c r="K76" s="55"/>
     </row>
     <row r="77" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A77" s="22"/>
@@ -3832,10 +3968,10 @@
       <c r="K77" s="24"/>
     </row>
     <row r="78" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A78" s="43" t="s">
+      <c r="A78" s="53" t="s">
         <v>148</v>
       </c>
-      <c r="B78" s="44"/>
+      <c r="B78" s="54"/>
       <c r="C78" s="18" t="s">
         <v>149</v>
       </c>
@@ -3845,20 +3981,22 @@
       <c r="E78" s="2" t="s">
         <v>151</v>
       </c>
-      <c r="F78" s="63" t="s">
+      <c r="F78" s="74" t="s">
         <v>152</v>
       </c>
-      <c r="G78" s="64"/>
-      <c r="H78" s="65"/>
-      <c r="I78" s="66"/>
-      <c r="J78" s="65"/>
-      <c r="K78" s="66"/>
+      <c r="G78" s="75"/>
+      <c r="H78" s="76"/>
+      <c r="I78" s="77"/>
+      <c r="J78" s="81" t="s">
+        <v>298</v>
+      </c>
+      <c r="K78" s="82"/>
     </row>
     <row r="79" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A79" s="43" t="s">
+      <c r="A79" s="53" t="s">
         <v>153</v>
       </c>
-      <c r="B79" s="44"/>
+      <c r="B79" s="54"/>
       <c r="C79" s="18" t="s">
         <v>149</v>
       </c>
@@ -3868,20 +4006,22 @@
       <c r="E79" s="2" t="s">
         <v>151</v>
       </c>
-      <c r="F79" s="63" t="s">
+      <c r="F79" s="74" t="s">
         <v>155</v>
       </c>
-      <c r="G79" s="64"/>
-      <c r="H79" s="65"/>
-      <c r="I79" s="66"/>
-      <c r="J79" s="65"/>
-      <c r="K79" s="66"/>
+      <c r="G79" s="75"/>
+      <c r="H79" s="76"/>
+      <c r="I79" s="77"/>
+      <c r="J79" s="81" t="s">
+        <v>298</v>
+      </c>
+      <c r="K79" s="82"/>
     </row>
     <row r="80" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A80" s="43" t="s">
+      <c r="A80" s="53" t="s">
         <v>156</v>
       </c>
-      <c r="B80" s="44"/>
+      <c r="B80" s="54"/>
       <c r="C80" s="18" t="s">
         <v>149</v>
       </c>
@@ -3891,20 +4031,22 @@
       <c r="E80" s="2" t="s">
         <v>151</v>
       </c>
-      <c r="F80" s="63" t="s">
+      <c r="F80" s="74" t="s">
         <v>158</v>
       </c>
-      <c r="G80" s="64"/>
-      <c r="H80" s="65"/>
-      <c r="I80" s="66"/>
-      <c r="J80" s="65"/>
-      <c r="K80" s="66"/>
+      <c r="G80" s="75"/>
+      <c r="H80" s="76"/>
+      <c r="I80" s="77"/>
+      <c r="J80" s="81" t="s">
+        <v>298</v>
+      </c>
+      <c r="K80" s="82"/>
     </row>
     <row r="81" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A81" s="43" t="s">
+      <c r="A81" s="53" t="s">
         <v>159</v>
       </c>
-      <c r="B81" s="44"/>
+      <c r="B81" s="54"/>
       <c r="C81" s="18" t="s">
         <v>149</v>
       </c>
@@ -3914,20 +4056,22 @@
       <c r="E81" s="2" t="s">
         <v>151</v>
       </c>
-      <c r="F81" s="63" t="s">
+      <c r="F81" s="74" t="s">
         <v>160</v>
       </c>
-      <c r="G81" s="64"/>
-      <c r="H81" s="65"/>
-      <c r="I81" s="66"/>
-      <c r="J81" s="65"/>
-      <c r="K81" s="66"/>
+      <c r="G81" s="75"/>
+      <c r="H81" s="76"/>
+      <c r="I81" s="77"/>
+      <c r="J81" s="81" t="s">
+        <v>298</v>
+      </c>
+      <c r="K81" s="82"/>
     </row>
     <row r="82" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A82" s="48" t="s">
+      <c r="A82" s="58" t="s">
         <v>161</v>
       </c>
-      <c r="B82" s="45"/>
+      <c r="B82" s="59"/>
       <c r="C82" s="18" t="s">
         <v>149</v>
       </c>
@@ -3937,20 +4081,22 @@
       <c r="E82" s="2" t="s">
         <v>151</v>
       </c>
-      <c r="F82" s="49" t="s">
+      <c r="F82" s="63" t="s">
         <v>163</v>
       </c>
-      <c r="G82" s="45"/>
-      <c r="H82" s="45"/>
-      <c r="I82" s="45"/>
-      <c r="J82" s="45"/>
-      <c r="K82" s="45"/>
+      <c r="G82" s="59"/>
+      <c r="H82" s="59"/>
+      <c r="I82" s="59"/>
+      <c r="J82" s="81" t="s">
+        <v>298</v>
+      </c>
+      <c r="K82" s="82"/>
     </row>
     <row r="83" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A83" s="48" t="s">
+      <c r="A83" s="58" t="s">
         <v>164</v>
       </c>
-      <c r="B83" s="45"/>
+      <c r="B83" s="59"/>
       <c r="C83" s="18" t="s">
         <v>149</v>
       </c>
@@ -3960,20 +4106,22 @@
       <c r="E83" s="2" t="s">
         <v>151</v>
       </c>
-      <c r="F83" s="49" t="s">
+      <c r="F83" s="63" t="s">
         <v>166</v>
       </c>
-      <c r="G83" s="45"/>
-      <c r="H83" s="45"/>
-      <c r="I83" s="45"/>
-      <c r="J83" s="45"/>
-      <c r="K83" s="45"/>
+      <c r="G83" s="59"/>
+      <c r="H83" s="59"/>
+      <c r="I83" s="59"/>
+      <c r="J83" s="81" t="s">
+        <v>298</v>
+      </c>
+      <c r="K83" s="82"/>
     </row>
     <row r="84" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A84" s="48" t="s">
+      <c r="A84" s="58" t="s">
         <v>167</v>
       </c>
-      <c r="B84" s="45"/>
+      <c r="B84" s="59"/>
       <c r="C84" s="18" t="s">
         <v>149</v>
       </c>
@@ -3983,14 +4131,16 @@
       <c r="E84" s="2" t="s">
         <v>151</v>
       </c>
-      <c r="F84" s="49" t="s">
+      <c r="F84" s="63" t="s">
         <v>169</v>
       </c>
-      <c r="G84" s="45"/>
-      <c r="H84" s="45"/>
-      <c r="I84" s="45"/>
-      <c r="J84" s="45"/>
-      <c r="K84" s="45"/>
+      <c r="G84" s="59"/>
+      <c r="H84" s="59"/>
+      <c r="I84" s="59"/>
+      <c r="J84" s="81" t="s">
+        <v>298</v>
+      </c>
+      <c r="K84" s="82"/>
     </row>
     <row r="85" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A85" s="19"/>
@@ -4006,67 +4156,67 @@
       <c r="K85" s="21"/>
     </row>
     <row r="86" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A86" s="31" t="s">
+      <c r="A86" s="41" t="s">
         <v>170</v>
       </c>
-      <c r="B86" s="32"/>
+      <c r="B86" s="42"/>
       <c r="C86" s="18" t="s">
         <v>171</v>
       </c>
       <c r="D86" s="2" t="s">
         <v>172</v>
       </c>
-      <c r="E86" s="37" t="s">
+      <c r="E86" s="47" t="s">
         <v>173</v>
       </c>
-      <c r="F86" s="31" t="s">
+      <c r="F86" s="41" t="s">
         <v>174</v>
       </c>
-      <c r="G86" s="32"/>
-      <c r="H86" s="25"/>
-      <c r="I86" s="26"/>
-      <c r="J86" s="25"/>
-      <c r="K86" s="26"/>
+      <c r="G86" s="42"/>
+      <c r="H86" s="35"/>
+      <c r="I86" s="36"/>
+      <c r="J86" s="35"/>
+      <c r="K86" s="36"/>
     </row>
     <row r="87" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A87" s="33"/>
-      <c r="B87" s="34"/>
+      <c r="A87" s="43"/>
+      <c r="B87" s="44"/>
       <c r="C87" s="18" t="s">
         <v>175</v>
       </c>
       <c r="D87" s="2" t="s">
         <v>154</v>
       </c>
-      <c r="E87" s="38"/>
-      <c r="F87" s="33"/>
-      <c r="G87" s="34"/>
-      <c r="H87" s="27"/>
-      <c r="I87" s="28"/>
-      <c r="J87" s="27"/>
-      <c r="K87" s="28"/>
+      <c r="E87" s="48"/>
+      <c r="F87" s="43"/>
+      <c r="G87" s="44"/>
+      <c r="H87" s="37"/>
+      <c r="I87" s="38"/>
+      <c r="J87" s="37"/>
+      <c r="K87" s="38"/>
     </row>
     <row r="88" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A88" s="35"/>
-      <c r="B88" s="36"/>
+      <c r="A88" s="45"/>
+      <c r="B88" s="46"/>
       <c r="C88" s="18" t="s">
         <v>176</v>
       </c>
       <c r="D88" s="2" t="s">
         <v>177</v>
       </c>
-      <c r="E88" s="39"/>
-      <c r="F88" s="35"/>
-      <c r="G88" s="36"/>
-      <c r="H88" s="29"/>
-      <c r="I88" s="30"/>
-      <c r="J88" s="29"/>
-      <c r="K88" s="30"/>
+      <c r="E88" s="49"/>
+      <c r="F88" s="45"/>
+      <c r="G88" s="46"/>
+      <c r="H88" s="39"/>
+      <c r="I88" s="40"/>
+      <c r="J88" s="39"/>
+      <c r="K88" s="40"/>
     </row>
     <row r="89" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A89" s="48" t="s">
+      <c r="A89" s="58" t="s">
         <v>178</v>
       </c>
-      <c r="B89" s="45"/>
+      <c r="B89" s="59"/>
       <c r="C89" s="18" t="s">
         <v>171</v>
       </c>
@@ -4076,20 +4226,20 @@
       <c r="E89" s="2" t="s">
         <v>180</v>
       </c>
-      <c r="F89" s="49" t="s">
+      <c r="F89" s="63" t="s">
         <v>181</v>
       </c>
-      <c r="G89" s="45"/>
-      <c r="H89" s="45"/>
-      <c r="I89" s="45"/>
-      <c r="J89" s="45"/>
-      <c r="K89" s="45"/>
+      <c r="G89" s="59"/>
+      <c r="H89" s="59"/>
+      <c r="I89" s="59"/>
+      <c r="J89" s="59"/>
+      <c r="K89" s="59"/>
     </row>
     <row r="90" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A90" s="48" t="s">
+      <c r="A90" s="58" t="s">
         <v>182</v>
       </c>
-      <c r="B90" s="45"/>
+      <c r="B90" s="59"/>
       <c r="C90" s="18" t="s">
         <v>50</v>
       </c>
@@ -4099,20 +4249,20 @@
       <c r="E90" s="2" t="s">
         <v>184</v>
       </c>
-      <c r="F90" s="49" t="s">
+      <c r="F90" s="63" t="s">
         <v>185</v>
       </c>
-      <c r="G90" s="45"/>
-      <c r="H90" s="45"/>
-      <c r="I90" s="45"/>
-      <c r="J90" s="45"/>
-      <c r="K90" s="45"/>
+      <c r="G90" s="59"/>
+      <c r="H90" s="59"/>
+      <c r="I90" s="59"/>
+      <c r="J90" s="59"/>
+      <c r="K90" s="59"/>
     </row>
     <row r="91" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A91" s="48" t="s">
+      <c r="A91" s="58" t="s">
         <v>186</v>
       </c>
-      <c r="B91" s="45"/>
+      <c r="B91" s="59"/>
       <c r="C91" s="18" t="s">
         <v>50</v>
       </c>
@@ -4122,20 +4272,20 @@
       <c r="E91" s="2" t="s">
         <v>184</v>
       </c>
-      <c r="F91" s="49" t="s">
+      <c r="F91" s="63" t="s">
         <v>188</v>
       </c>
-      <c r="G91" s="45"/>
-      <c r="H91" s="45"/>
-      <c r="I91" s="45"/>
-      <c r="J91" s="45"/>
-      <c r="K91" s="45"/>
+      <c r="G91" s="59"/>
+      <c r="H91" s="59"/>
+      <c r="I91" s="59"/>
+      <c r="J91" s="59"/>
+      <c r="K91" s="59"/>
     </row>
     <row r="92" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A92" s="48" t="s">
+      <c r="A92" s="58" t="s">
         <v>189</v>
       </c>
-      <c r="B92" s="45"/>
+      <c r="B92" s="59"/>
       <c r="C92" s="18" t="s">
         <v>171</v>
       </c>
@@ -4145,20 +4295,20 @@
       <c r="E92" s="2" t="s">
         <v>173</v>
       </c>
-      <c r="F92" s="49" t="s">
+      <c r="F92" s="63" t="s">
         <v>84</v>
       </c>
-      <c r="G92" s="45"/>
-      <c r="H92" s="45"/>
-      <c r="I92" s="45"/>
-      <c r="J92" s="45"/>
-      <c r="K92" s="45"/>
+      <c r="G92" s="59"/>
+      <c r="H92" s="59"/>
+      <c r="I92" s="59"/>
+      <c r="J92" s="59"/>
+      <c r="K92" s="59"/>
     </row>
     <row r="93" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A93" s="48" t="s">
+      <c r="A93" s="58" t="s">
         <v>190</v>
       </c>
-      <c r="B93" s="45"/>
+      <c r="B93" s="59"/>
       <c r="C93" s="18" t="s">
         <v>191</v>
       </c>
@@ -4168,14 +4318,14 @@
       <c r="E93" s="2" t="s">
         <v>151</v>
       </c>
-      <c r="F93" s="49" t="s">
+      <c r="F93" s="63" t="s">
         <v>193</v>
       </c>
-      <c r="G93" s="45"/>
-      <c r="H93" s="45"/>
-      <c r="I93" s="45"/>
-      <c r="J93" s="45"/>
-      <c r="K93" s="45"/>
+      <c r="G93" s="59"/>
+      <c r="H93" s="59"/>
+      <c r="I93" s="59"/>
+      <c r="J93" s="59"/>
+      <c r="K93" s="59"/>
     </row>
     <row r="94" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A94" s="19"/>
@@ -4191,124 +4341,124 @@
       <c r="K94" s="21"/>
     </row>
     <row r="95" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A95" s="31" t="s">
+      <c r="A95" s="41" t="s">
         <v>194</v>
       </c>
-      <c r="B95" s="32"/>
+      <c r="B95" s="42"/>
       <c r="C95" s="18" t="s">
         <v>195</v>
       </c>
       <c r="D95" s="2" t="s">
         <v>196</v>
       </c>
-      <c r="E95" s="37" t="s">
+      <c r="E95" s="47" t="s">
         <v>197</v>
       </c>
-      <c r="F95" s="31" t="s">
+      <c r="F95" s="41" t="s">
         <v>198</v>
       </c>
-      <c r="G95" s="32"/>
-      <c r="H95" s="25"/>
-      <c r="I95" s="26"/>
-      <c r="J95" s="25"/>
-      <c r="K95" s="26"/>
+      <c r="G95" s="42"/>
+      <c r="H95" s="35"/>
+      <c r="I95" s="36"/>
+      <c r="J95" s="35"/>
+      <c r="K95" s="36"/>
     </row>
     <row r="96" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A96" s="33"/>
-      <c r="B96" s="34"/>
+      <c r="A96" s="43"/>
+      <c r="B96" s="44"/>
       <c r="C96" s="18" t="s">
         <v>199</v>
       </c>
       <c r="D96" s="2" t="s">
         <v>200</v>
       </c>
-      <c r="E96" s="38"/>
-      <c r="F96" s="33"/>
-      <c r="G96" s="34"/>
-      <c r="H96" s="27"/>
-      <c r="I96" s="28"/>
-      <c r="J96" s="27"/>
-      <c r="K96" s="28"/>
+      <c r="E96" s="48"/>
+      <c r="F96" s="43"/>
+      <c r="G96" s="44"/>
+      <c r="H96" s="37"/>
+      <c r="I96" s="38"/>
+      <c r="J96" s="37"/>
+      <c r="K96" s="38"/>
     </row>
     <row r="97" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A97" s="33"/>
-      <c r="B97" s="34"/>
+      <c r="A97" s="43"/>
+      <c r="B97" s="44"/>
       <c r="C97" s="18" t="s">
         <v>201</v>
       </c>
       <c r="D97" s="2" t="s">
         <v>202</v>
       </c>
-      <c r="E97" s="38"/>
-      <c r="F97" s="33"/>
-      <c r="G97" s="34"/>
-      <c r="H97" s="27"/>
-      <c r="I97" s="28"/>
-      <c r="J97" s="27"/>
-      <c r="K97" s="28"/>
+      <c r="E97" s="48"/>
+      <c r="F97" s="43"/>
+      <c r="G97" s="44"/>
+      <c r="H97" s="37"/>
+      <c r="I97" s="38"/>
+      <c r="J97" s="37"/>
+      <c r="K97" s="38"/>
     </row>
     <row r="98" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A98" s="35"/>
-      <c r="B98" s="36"/>
+      <c r="A98" s="45"/>
+      <c r="B98" s="46"/>
       <c r="C98" s="18" t="s">
         <v>203</v>
       </c>
       <c r="D98" s="2" t="s">
         <v>204</v>
       </c>
-      <c r="E98" s="39"/>
-      <c r="F98" s="35"/>
-      <c r="G98" s="36"/>
-      <c r="H98" s="29"/>
-      <c r="I98" s="30"/>
-      <c r="J98" s="29"/>
-      <c r="K98" s="30"/>
+      <c r="E98" s="49"/>
+      <c r="F98" s="45"/>
+      <c r="G98" s="46"/>
+      <c r="H98" s="39"/>
+      <c r="I98" s="40"/>
+      <c r="J98" s="39"/>
+      <c r="K98" s="40"/>
     </row>
     <row r="99" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A99" s="31" t="s">
+      <c r="A99" s="41" t="s">
         <v>205</v>
       </c>
-      <c r="B99" s="32"/>
+      <c r="B99" s="42"/>
       <c r="C99" s="18" t="s">
         <v>195</v>
       </c>
       <c r="D99" s="2" t="s">
         <v>206</v>
       </c>
-      <c r="E99" s="37" t="s">
+      <c r="E99" s="47" t="s">
         <v>180</v>
       </c>
-      <c r="F99" s="31" t="s">
+      <c r="F99" s="41" t="s">
         <v>207</v>
       </c>
-      <c r="G99" s="32"/>
-      <c r="H99" s="25"/>
-      <c r="I99" s="26"/>
-      <c r="J99" s="25"/>
-      <c r="K99" s="26"/>
+      <c r="G99" s="42"/>
+      <c r="H99" s="35"/>
+      <c r="I99" s="36"/>
+      <c r="J99" s="35"/>
+      <c r="K99" s="36"/>
     </row>
     <row r="100" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A100" s="35"/>
-      <c r="B100" s="36"/>
+      <c r="A100" s="45"/>
+      <c r="B100" s="46"/>
       <c r="C100" s="18" t="s">
         <v>201</v>
       </c>
       <c r="D100" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="E100" s="39"/>
-      <c r="F100" s="35"/>
-      <c r="G100" s="36"/>
-      <c r="H100" s="29"/>
-      <c r="I100" s="30"/>
-      <c r="J100" s="29"/>
-      <c r="K100" s="30"/>
+      <c r="E100" s="49"/>
+      <c r="F100" s="45"/>
+      <c r="G100" s="46"/>
+      <c r="H100" s="39"/>
+      <c r="I100" s="40"/>
+      <c r="J100" s="39"/>
+      <c r="K100" s="40"/>
     </row>
     <row r="101" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A101" s="48" t="s">
+      <c r="A101" s="58" t="s">
         <v>208</v>
       </c>
-      <c r="B101" s="45"/>
+      <c r="B101" s="59"/>
       <c r="C101" s="18" t="s">
         <v>50</v>
       </c>
@@ -4318,20 +4468,20 @@
       <c r="E101" s="2" t="s">
         <v>209</v>
       </c>
-      <c r="F101" s="49" t="s">
+      <c r="F101" s="63" t="s">
         <v>210</v>
       </c>
-      <c r="G101" s="45"/>
-      <c r="H101" s="45"/>
-      <c r="I101" s="45"/>
-      <c r="J101" s="45"/>
-      <c r="K101" s="45"/>
+      <c r="G101" s="59"/>
+      <c r="H101" s="59"/>
+      <c r="I101" s="59"/>
+      <c r="J101" s="59"/>
+      <c r="K101" s="59"/>
     </row>
     <row r="102" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A102" s="48" t="s">
+      <c r="A102" s="58" t="s">
         <v>211</v>
       </c>
-      <c r="B102" s="45"/>
+      <c r="B102" s="59"/>
       <c r="C102" s="18" t="s">
         <v>203</v>
       </c>
@@ -4341,20 +4491,20 @@
       <c r="E102" s="2" t="s">
         <v>197</v>
       </c>
-      <c r="F102" s="49" t="s">
+      <c r="F102" s="63" t="s">
         <v>213</v>
       </c>
-      <c r="G102" s="45"/>
-      <c r="H102" s="45"/>
-      <c r="I102" s="45"/>
-      <c r="J102" s="45"/>
-      <c r="K102" s="45"/>
+      <c r="G102" s="59"/>
+      <c r="H102" s="59"/>
+      <c r="I102" s="59"/>
+      <c r="J102" s="59"/>
+      <c r="K102" s="59"/>
     </row>
     <row r="103" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A103" s="48" t="s">
+      <c r="A103" s="58" t="s">
         <v>214</v>
       </c>
-      <c r="B103" s="45"/>
+      <c r="B103" s="59"/>
       <c r="C103" s="18" t="s">
         <v>215</v>
       </c>
@@ -4364,20 +4514,20 @@
       <c r="E103" s="2" t="s">
         <v>217</v>
       </c>
-      <c r="F103" s="49" t="s">
+      <c r="F103" s="63" t="s">
         <v>218</v>
       </c>
-      <c r="G103" s="45"/>
-      <c r="H103" s="45"/>
-      <c r="I103" s="45"/>
-      <c r="J103" s="45"/>
-      <c r="K103" s="45"/>
+      <c r="G103" s="59"/>
+      <c r="H103" s="59"/>
+      <c r="I103" s="59"/>
+      <c r="J103" s="59"/>
+      <c r="K103" s="59"/>
     </row>
     <row r="104" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A104" s="48" t="s">
+      <c r="A104" s="58" t="s">
         <v>219</v>
       </c>
-      <c r="B104" s="45"/>
+      <c r="B104" s="59"/>
       <c r="C104" s="18" t="s">
         <v>220</v>
       </c>
@@ -4387,14 +4537,14 @@
       <c r="E104" s="2" t="s">
         <v>221</v>
       </c>
-      <c r="F104" s="49" t="s">
+      <c r="F104" s="63" t="s">
         <v>222</v>
       </c>
-      <c r="G104" s="45"/>
-      <c r="H104" s="45"/>
-      <c r="I104" s="45"/>
-      <c r="J104" s="45"/>
-      <c r="K104" s="45"/>
+      <c r="G104" s="59"/>
+      <c r="H104" s="59"/>
+      <c r="I104" s="59"/>
+      <c r="J104" s="59"/>
+      <c r="K104" s="59"/>
     </row>
     <row r="105" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A105" s="19"/>
@@ -4410,10 +4560,10 @@
       <c r="K105" s="21"/>
     </row>
     <row r="106" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A106" s="48" t="s">
+      <c r="A106" s="58" t="s">
         <v>223</v>
       </c>
-      <c r="B106" s="45"/>
+      <c r="B106" s="59"/>
       <c r="C106" s="18" t="s">
         <v>224</v>
       </c>
@@ -4423,20 +4573,22 @@
       <c r="E106" s="2" t="s">
         <v>226</v>
       </c>
-      <c r="F106" s="49" t="s">
+      <c r="F106" s="63" t="s">
         <v>227</v>
       </c>
-      <c r="G106" s="45"/>
-      <c r="H106" s="45"/>
-      <c r="I106" s="45"/>
-      <c r="J106" s="45"/>
-      <c r="K106" s="45"/>
+      <c r="G106" s="59"/>
+      <c r="H106" s="59"/>
+      <c r="I106" s="59"/>
+      <c r="J106" s="55" t="s">
+        <v>298</v>
+      </c>
+      <c r="K106" s="55"/>
     </row>
     <row r="107" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A107" s="48" t="s">
+      <c r="A107" s="58" t="s">
         <v>228</v>
       </c>
-      <c r="B107" s="45"/>
+      <c r="B107" s="59"/>
       <c r="C107" s="18" t="s">
         <v>224</v>
       </c>
@@ -4446,20 +4598,22 @@
       <c r="E107" s="2" t="s">
         <v>226</v>
       </c>
-      <c r="F107" s="49" t="s">
+      <c r="F107" s="63" t="s">
         <v>227</v>
       </c>
-      <c r="G107" s="45"/>
-      <c r="H107" s="45"/>
-      <c r="I107" s="45"/>
-      <c r="J107" s="45"/>
-      <c r="K107" s="45"/>
+      <c r="G107" s="59"/>
+      <c r="H107" s="59"/>
+      <c r="I107" s="59"/>
+      <c r="J107" s="55" t="s">
+        <v>298</v>
+      </c>
+      <c r="K107" s="55"/>
     </row>
     <row r="108" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A108" s="48" t="s">
+      <c r="A108" s="58" t="s">
         <v>230</v>
       </c>
-      <c r="B108" s="45"/>
+      <c r="B108" s="59"/>
       <c r="C108" s="18" t="s">
         <v>224</v>
       </c>
@@ -4469,20 +4623,22 @@
       <c r="E108" s="2" t="s">
         <v>226</v>
       </c>
-      <c r="F108" s="49" t="s">
+      <c r="F108" s="63" t="s">
         <v>227</v>
       </c>
-      <c r="G108" s="45"/>
-      <c r="H108" s="45"/>
-      <c r="I108" s="45"/>
-      <c r="J108" s="45"/>
-      <c r="K108" s="45"/>
+      <c r="G108" s="59"/>
+      <c r="H108" s="59"/>
+      <c r="I108" s="59"/>
+      <c r="J108" s="55" t="s">
+        <v>298</v>
+      </c>
+      <c r="K108" s="55"/>
     </row>
     <row r="109" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A109" s="48" t="s">
+      <c r="A109" s="58" t="s">
         <v>232</v>
       </c>
-      <c r="B109" s="45"/>
+      <c r="B109" s="59"/>
       <c r="C109" s="18" t="s">
         <v>224</v>
       </c>
@@ -4492,20 +4648,22 @@
       <c r="E109" s="2" t="s">
         <v>226</v>
       </c>
-      <c r="F109" s="49" t="s">
+      <c r="F109" s="63" t="s">
         <v>227</v>
       </c>
-      <c r="G109" s="45"/>
-      <c r="H109" s="45"/>
-      <c r="I109" s="45"/>
-      <c r="J109" s="45"/>
-      <c r="K109" s="45"/>
+      <c r="G109" s="59"/>
+      <c r="H109" s="59"/>
+      <c r="I109" s="59"/>
+      <c r="J109" s="55" t="s">
+        <v>298</v>
+      </c>
+      <c r="K109" s="55"/>
     </row>
     <row r="110" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A110" s="48" t="s">
+      <c r="A110" s="58" t="s">
         <v>234</v>
       </c>
-      <c r="B110" s="45"/>
+      <c r="B110" s="59"/>
       <c r="C110" s="18" t="s">
         <v>224</v>
       </c>
@@ -4515,20 +4673,22 @@
       <c r="E110" s="2" t="s">
         <v>226</v>
       </c>
-      <c r="F110" s="49" t="s">
+      <c r="F110" s="63" t="s">
         <v>227</v>
       </c>
-      <c r="G110" s="45"/>
-      <c r="H110" s="45"/>
-      <c r="I110" s="45"/>
-      <c r="J110" s="45"/>
-      <c r="K110" s="45"/>
+      <c r="G110" s="59"/>
+      <c r="H110" s="59"/>
+      <c r="I110" s="59"/>
+      <c r="J110" s="55" t="s">
+        <v>298</v>
+      </c>
+      <c r="K110" s="55"/>
     </row>
     <row r="111" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A111" s="48" t="s">
+      <c r="A111" s="58" t="s">
         <v>236</v>
       </c>
-      <c r="B111" s="45"/>
+      <c r="B111" s="59"/>
       <c r="C111" s="18" t="s">
         <v>224</v>
       </c>
@@ -4538,20 +4698,22 @@
       <c r="E111" s="2" t="s">
         <v>226</v>
       </c>
-      <c r="F111" s="49" t="s">
+      <c r="F111" s="63" t="s">
         <v>238</v>
       </c>
-      <c r="G111" s="45"/>
-      <c r="H111" s="45"/>
-      <c r="I111" s="45"/>
-      <c r="J111" s="45"/>
-      <c r="K111" s="45"/>
+      <c r="G111" s="59"/>
+      <c r="H111" s="59"/>
+      <c r="I111" s="59"/>
+      <c r="J111" s="55" t="s">
+        <v>298</v>
+      </c>
+      <c r="K111" s="55"/>
     </row>
     <row r="112" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A112" s="48" t="s">
+      <c r="A112" s="58" t="s">
         <v>239</v>
       </c>
-      <c r="B112" s="45"/>
+      <c r="B112" s="59"/>
       <c r="C112" s="18" t="s">
         <v>141</v>
       </c>
@@ -4561,20 +4723,22 @@
       <c r="E112" s="2" t="s">
         <v>143</v>
       </c>
-      <c r="F112" s="49" t="s">
+      <c r="F112" s="63" t="s">
         <v>241</v>
       </c>
-      <c r="G112" s="45"/>
-      <c r="H112" s="45"/>
-      <c r="I112" s="45"/>
-      <c r="J112" s="45"/>
-      <c r="K112" s="45"/>
+      <c r="G112" s="59"/>
+      <c r="H112" s="59"/>
+      <c r="I112" s="59"/>
+      <c r="J112" s="55" t="s">
+        <v>298</v>
+      </c>
+      <c r="K112" s="55"/>
     </row>
     <row r="113" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A113" s="48" t="s">
+      <c r="A113" s="58" t="s">
         <v>242</v>
       </c>
-      <c r="B113" s="45"/>
+      <c r="B113" s="59"/>
       <c r="C113" s="18" t="s">
         <v>220</v>
       </c>
@@ -4584,20 +4748,22 @@
       <c r="E113" s="2" t="s">
         <v>243</v>
       </c>
-      <c r="F113" s="49" t="s">
+      <c r="F113" s="63" t="s">
         <v>244</v>
       </c>
-      <c r="G113" s="45"/>
-      <c r="H113" s="45"/>
-      <c r="I113" s="45"/>
-      <c r="J113" s="45"/>
-      <c r="K113" s="45"/>
+      <c r="G113" s="59"/>
+      <c r="H113" s="59"/>
+      <c r="I113" s="59"/>
+      <c r="J113" s="78" t="s">
+        <v>299</v>
+      </c>
+      <c r="K113" s="78"/>
     </row>
     <row r="114" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A114" s="48" t="s">
+      <c r="A114" s="58" t="s">
         <v>245</v>
       </c>
-      <c r="B114" s="45"/>
+      <c r="B114" s="59"/>
       <c r="C114" s="18" t="s">
         <v>220</v>
       </c>
@@ -4607,20 +4773,22 @@
       <c r="E114" s="2" t="s">
         <v>243</v>
       </c>
-      <c r="F114" s="49" t="s">
+      <c r="F114" s="63" t="s">
         <v>246</v>
       </c>
-      <c r="G114" s="45"/>
-      <c r="H114" s="45"/>
-      <c r="I114" s="45"/>
-      <c r="J114" s="45"/>
-      <c r="K114" s="45"/>
+      <c r="G114" s="59"/>
+      <c r="H114" s="59"/>
+      <c r="I114" s="59"/>
+      <c r="J114" s="55" t="s">
+        <v>298</v>
+      </c>
+      <c r="K114" s="55"/>
     </row>
     <row r="115" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A115" s="48" t="s">
+      <c r="A115" s="58" t="s">
         <v>247</v>
       </c>
-      <c r="B115" s="45"/>
+      <c r="B115" s="59"/>
       <c r="C115" s="18" t="s">
         <v>248</v>
       </c>
@@ -4630,14 +4798,16 @@
       <c r="E115" s="2" t="s">
         <v>250</v>
       </c>
-      <c r="F115" s="49" t="s">
+      <c r="F115" s="63" t="s">
         <v>251</v>
       </c>
-      <c r="G115" s="45"/>
-      <c r="H115" s="45"/>
-      <c r="I115" s="45"/>
-      <c r="J115" s="45"/>
-      <c r="K115" s="45"/>
+      <c r="G115" s="59"/>
+      <c r="H115" s="59"/>
+      <c r="I115" s="59"/>
+      <c r="J115" s="55" t="s">
+        <v>298</v>
+      </c>
+      <c r="K115" s="55"/>
     </row>
     <row r="116" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A116" s="19"/>
@@ -4653,10 +4823,10 @@
       <c r="K116" s="21"/>
     </row>
     <row r="117" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A117" s="48" t="s">
+      <c r="A117" s="58" t="s">
         <v>252</v>
       </c>
-      <c r="B117" s="45"/>
+      <c r="B117" s="59"/>
       <c r="C117" s="18" t="s">
         <v>39</v>
       </c>
@@ -4666,20 +4836,20 @@
       <c r="E117" s="2" t="s">
         <v>254</v>
       </c>
-      <c r="F117" s="49" t="s">
+      <c r="F117" s="63" t="s">
         <v>255</v>
       </c>
-      <c r="G117" s="45"/>
-      <c r="H117" s="45"/>
-      <c r="I117" s="45"/>
-      <c r="J117" s="45"/>
-      <c r="K117" s="45"/>
+      <c r="G117" s="59"/>
+      <c r="H117" s="59"/>
+      <c r="I117" s="59"/>
+      <c r="J117" s="59"/>
+      <c r="K117" s="59"/>
     </row>
     <row r="118" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A118" s="48" t="s">
+      <c r="A118" s="58" t="s">
         <v>256</v>
       </c>
-      <c r="B118" s="45"/>
+      <c r="B118" s="59"/>
       <c r="C118" s="18" t="s">
         <v>39</v>
       </c>
@@ -4689,20 +4859,20 @@
       <c r="E118" s="2" t="s">
         <v>254</v>
       </c>
-      <c r="F118" s="49" t="s">
+      <c r="F118" s="63" t="s">
         <v>258</v>
       </c>
-      <c r="G118" s="45"/>
-      <c r="H118" s="45"/>
-      <c r="I118" s="45"/>
-      <c r="J118" s="45"/>
-      <c r="K118" s="45"/>
+      <c r="G118" s="59"/>
+      <c r="H118" s="59"/>
+      <c r="I118" s="59"/>
+      <c r="J118" s="59"/>
+      <c r="K118" s="59"/>
     </row>
     <row r="119" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A119" s="48" t="s">
+      <c r="A119" s="58" t="s">
         <v>259</v>
       </c>
-      <c r="B119" s="45"/>
+      <c r="B119" s="59"/>
       <c r="C119" s="18" t="s">
         <v>260</v>
       </c>
@@ -4712,20 +4882,20 @@
       <c r="E119" s="2" t="s">
         <v>143</v>
       </c>
-      <c r="F119" s="49" t="s">
+      <c r="F119" s="63" t="s">
         <v>262</v>
       </c>
-      <c r="G119" s="45"/>
-      <c r="H119" s="45"/>
-      <c r="I119" s="45"/>
-      <c r="J119" s="45"/>
-      <c r="K119" s="45"/>
+      <c r="G119" s="59"/>
+      <c r="H119" s="59"/>
+      <c r="I119" s="59"/>
+      <c r="J119" s="59"/>
+      <c r="K119" s="59"/>
     </row>
     <row r="120" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A120" s="48" t="s">
+      <c r="A120" s="58" t="s">
         <v>263</v>
       </c>
-      <c r="B120" s="45"/>
+      <c r="B120" s="59"/>
       <c r="C120" s="18" t="s">
         <v>141</v>
       </c>
@@ -4735,14 +4905,14 @@
       <c r="E120" s="2" t="s">
         <v>143</v>
       </c>
-      <c r="F120" s="49" t="s">
+      <c r="F120" s="63" t="s">
         <v>265</v>
       </c>
-      <c r="G120" s="45"/>
-      <c r="H120" s="45"/>
-      <c r="I120" s="45"/>
-      <c r="J120" s="45"/>
-      <c r="K120" s="45"/>
+      <c r="G120" s="59"/>
+      <c r="H120" s="59"/>
+      <c r="I120" s="59"/>
+      <c r="J120" s="59"/>
+      <c r="K120" s="59"/>
     </row>
     <row r="121" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A121" s="19"/>
@@ -4758,10 +4928,10 @@
       <c r="K121" s="21"/>
     </row>
     <row r="122" spans="1:11" ht="30" x14ac:dyDescent="0.25">
-      <c r="A122" s="48" t="s">
+      <c r="A122" s="58" t="s">
         <v>266</v>
       </c>
-      <c r="B122" s="45"/>
+      <c r="B122" s="59"/>
       <c r="C122" s="18" t="s">
         <v>39</v>
       </c>
@@ -4771,20 +4941,22 @@
       <c r="E122" s="2" t="s">
         <v>243</v>
       </c>
-      <c r="F122" s="49" t="s">
+      <c r="F122" s="63" t="s">
         <v>268</v>
       </c>
-      <c r="G122" s="45"/>
-      <c r="H122" s="45"/>
-      <c r="I122" s="45"/>
-      <c r="J122" s="45"/>
-      <c r="K122" s="45"/>
+      <c r="G122" s="59"/>
+      <c r="H122" s="59"/>
+      <c r="I122" s="59"/>
+      <c r="J122" s="55" t="s">
+        <v>298</v>
+      </c>
+      <c r="K122" s="55"/>
     </row>
     <row r="123" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A123" s="48" t="s">
+      <c r="A123" s="58" t="s">
         <v>269</v>
       </c>
-      <c r="B123" s="45"/>
+      <c r="B123" s="59"/>
       <c r="C123" s="18" t="s">
         <v>39</v>
       </c>
@@ -4794,17 +4966,44 @@
       <c r="E123" s="2" t="s">
         <v>243</v>
       </c>
-      <c r="F123" s="49" t="s">
+      <c r="F123" s="63" t="s">
         <v>271</v>
       </c>
-      <c r="G123" s="45"/>
-      <c r="H123" s="45"/>
-      <c r="I123" s="45"/>
-      <c r="J123" s="45"/>
-      <c r="K123" s="45"/>
+      <c r="G123" s="59"/>
+      <c r="H123" s="59"/>
+      <c r="I123" s="59"/>
+      <c r="J123" s="55" t="s">
+        <v>298</v>
+      </c>
+      <c r="K123" s="55"/>
+    </row>
+    <row r="124" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A124" s="25" t="s">
+        <v>516</v>
+      </c>
+      <c r="B124" s="26"/>
+      <c r="C124" s="18" t="s">
+        <v>39</v>
+      </c>
+      <c r="D124" s="2" t="s">
+        <v>515</v>
+      </c>
+      <c r="E124" s="2" t="s">
+        <v>243</v>
+      </c>
+      <c r="F124" s="25" t="s">
+        <v>514</v>
+      </c>
+      <c r="G124" s="26"/>
+      <c r="H124" s="25"/>
+      <c r="I124" s="26"/>
+      <c r="J124" s="27" t="s">
+        <v>298</v>
+      </c>
+      <c r="K124" s="28"/>
     </row>
   </sheetData>
-  <mergeCells count="335">
+  <mergeCells count="339">
     <mergeCell ref="J110:K110"/>
     <mergeCell ref="J107:K107"/>
     <mergeCell ref="H84:I84"/>
@@ -4901,6 +5100,8 @@
     <mergeCell ref="F29:G29"/>
     <mergeCell ref="H49:I49"/>
     <mergeCell ref="A35:B35"/>
+    <mergeCell ref="A99:B100"/>
+    <mergeCell ref="E99:E100"/>
     <mergeCell ref="J122:K122"/>
     <mergeCell ref="C6:E6"/>
     <mergeCell ref="A102:B102"/>
@@ -4923,26 +5124,6 @@
     <mergeCell ref="J29:K29"/>
     <mergeCell ref="J48:K48"/>
     <mergeCell ref="J102:K102"/>
-    <mergeCell ref="J80:K80"/>
-    <mergeCell ref="J55:K55"/>
-    <mergeCell ref="F112:G112"/>
-    <mergeCell ref="A117:B117"/>
-    <mergeCell ref="F44:G44"/>
-    <mergeCell ref="H112:I112"/>
-    <mergeCell ref="A71:B71"/>
-    <mergeCell ref="F114:G114"/>
-    <mergeCell ref="A38:B38"/>
-    <mergeCell ref="F40:G40"/>
-    <mergeCell ref="F89:G89"/>
-    <mergeCell ref="H44:I44"/>
-    <mergeCell ref="F43:G43"/>
-    <mergeCell ref="F48:G48"/>
-    <mergeCell ref="F39:G39"/>
-    <mergeCell ref="F93:G93"/>
-    <mergeCell ref="H92:I92"/>
-    <mergeCell ref="F104:G104"/>
-    <mergeCell ref="F50:G51"/>
-    <mergeCell ref="H109:I109"/>
     <mergeCell ref="J109:K109"/>
     <mergeCell ref="J81:K81"/>
     <mergeCell ref="F79:G79"/>
@@ -4953,6 +5134,19 @@
     <mergeCell ref="J78:K78"/>
     <mergeCell ref="F58:G58"/>
     <mergeCell ref="J91:K91"/>
+    <mergeCell ref="H95:I98"/>
+    <mergeCell ref="J95:K98"/>
+    <mergeCell ref="F99:G100"/>
+    <mergeCell ref="H99:I100"/>
+    <mergeCell ref="J99:K100"/>
+    <mergeCell ref="F89:G89"/>
+    <mergeCell ref="F93:G93"/>
+    <mergeCell ref="H92:I92"/>
+    <mergeCell ref="F104:G104"/>
+    <mergeCell ref="F50:G51"/>
+    <mergeCell ref="H109:I109"/>
+    <mergeCell ref="J80:K80"/>
+    <mergeCell ref="J55:K55"/>
     <mergeCell ref="A6:B6"/>
     <mergeCell ref="J92:K92"/>
     <mergeCell ref="F57:G57"/>
@@ -4977,13 +5171,6 @@
     <mergeCell ref="H57:I57"/>
     <mergeCell ref="J60:K60"/>
     <mergeCell ref="A9:B9"/>
-    <mergeCell ref="F35:G35"/>
-    <mergeCell ref="J93:K93"/>
-    <mergeCell ref="F106:G106"/>
-    <mergeCell ref="F78:G78"/>
-    <mergeCell ref="H78:I78"/>
-    <mergeCell ref="H71:I71"/>
-    <mergeCell ref="F80:G80"/>
     <mergeCell ref="H122:I122"/>
     <mergeCell ref="A56:B56"/>
     <mergeCell ref="A42:B42"/>
@@ -4994,12 +5181,20 @@
     <mergeCell ref="H54:I54"/>
     <mergeCell ref="H115:I115"/>
     <mergeCell ref="H83:I83"/>
-    <mergeCell ref="E17:E18"/>
-    <mergeCell ref="A46:B47"/>
-    <mergeCell ref="A50:B51"/>
-    <mergeCell ref="A62:B64"/>
-    <mergeCell ref="F62:G64"/>
-    <mergeCell ref="H62:I64"/>
+    <mergeCell ref="E65:E67"/>
+    <mergeCell ref="F118:G118"/>
+    <mergeCell ref="H118:I118"/>
+    <mergeCell ref="H110:I110"/>
+    <mergeCell ref="A119:B119"/>
+    <mergeCell ref="H114:I114"/>
+    <mergeCell ref="F108:G108"/>
+    <mergeCell ref="F112:G112"/>
+    <mergeCell ref="A117:B117"/>
+    <mergeCell ref="F44:G44"/>
+    <mergeCell ref="H112:I112"/>
+    <mergeCell ref="A71:B71"/>
+    <mergeCell ref="F114:G114"/>
+    <mergeCell ref="H44:I44"/>
     <mergeCell ref="J123:K123"/>
     <mergeCell ref="J52:K52"/>
     <mergeCell ref="F92:G92"/>
@@ -5018,37 +5213,28 @@
     <mergeCell ref="J101:K101"/>
     <mergeCell ref="A90:B90"/>
     <mergeCell ref="A65:B67"/>
-    <mergeCell ref="E65:E67"/>
-    <mergeCell ref="F118:G118"/>
-    <mergeCell ref="H118:I118"/>
-    <mergeCell ref="H110:I110"/>
-    <mergeCell ref="A119:B119"/>
-    <mergeCell ref="H114:I114"/>
-    <mergeCell ref="F108:G108"/>
-    <mergeCell ref="J36:K36"/>
-    <mergeCell ref="F107:G107"/>
-    <mergeCell ref="H107:I107"/>
-    <mergeCell ref="F81:G81"/>
-    <mergeCell ref="H81:I81"/>
-    <mergeCell ref="A44:B44"/>
-    <mergeCell ref="J75:K75"/>
-    <mergeCell ref="J90:K90"/>
-    <mergeCell ref="H38:I38"/>
-    <mergeCell ref="F59:G59"/>
-    <mergeCell ref="A49:B49"/>
-    <mergeCell ref="J76:K76"/>
-    <mergeCell ref="A83:B83"/>
-    <mergeCell ref="A55:B55"/>
-    <mergeCell ref="A37:B37"/>
-    <mergeCell ref="A36:B36"/>
-    <mergeCell ref="A123:B123"/>
-    <mergeCell ref="F45:G45"/>
-    <mergeCell ref="H9:I10"/>
-    <mergeCell ref="J9:K10"/>
-    <mergeCell ref="F9:G10"/>
-    <mergeCell ref="A11:B12"/>
-    <mergeCell ref="A13:B14"/>
-    <mergeCell ref="A15:B16"/>
+    <mergeCell ref="J93:K93"/>
+    <mergeCell ref="F106:G106"/>
+    <mergeCell ref="F78:G78"/>
+    <mergeCell ref="H78:I78"/>
+    <mergeCell ref="H71:I71"/>
+    <mergeCell ref="F80:G80"/>
+    <mergeCell ref="J86:K88"/>
+    <mergeCell ref="A95:B98"/>
+    <mergeCell ref="E95:E98"/>
+    <mergeCell ref="F95:G98"/>
+    <mergeCell ref="E17:E18"/>
+    <mergeCell ref="A46:B47"/>
+    <mergeCell ref="A50:B51"/>
+    <mergeCell ref="A62:B64"/>
+    <mergeCell ref="F62:G64"/>
+    <mergeCell ref="H62:I64"/>
+    <mergeCell ref="F35:G35"/>
+    <mergeCell ref="A38:B38"/>
+    <mergeCell ref="F40:G40"/>
+    <mergeCell ref="F43:G43"/>
+    <mergeCell ref="F48:G48"/>
+    <mergeCell ref="F39:G39"/>
     <mergeCell ref="A17:B18"/>
     <mergeCell ref="A19:B20"/>
     <mergeCell ref="A21:B22"/>
@@ -5059,19 +5245,8 @@
     <mergeCell ref="E9:E10"/>
     <mergeCell ref="E13:E14"/>
     <mergeCell ref="E15:E16"/>
-    <mergeCell ref="J111:K111"/>
-    <mergeCell ref="J56:K56"/>
-    <mergeCell ref="J42:K42"/>
-    <mergeCell ref="J58:K58"/>
     <mergeCell ref="E19:E20"/>
     <mergeCell ref="E21:E22"/>
-    <mergeCell ref="H13:I14"/>
-    <mergeCell ref="H15:I16"/>
-    <mergeCell ref="H17:I18"/>
-    <mergeCell ref="H19:I20"/>
-    <mergeCell ref="H21:I22"/>
-    <mergeCell ref="J112:K112"/>
-    <mergeCell ref="J44:K44"/>
     <mergeCell ref="C5:E5"/>
     <mergeCell ref="A120:B120"/>
     <mergeCell ref="E23:E25"/>
@@ -5089,11 +5264,13 @@
     <mergeCell ref="J41:K41"/>
     <mergeCell ref="A79:B79"/>
     <mergeCell ref="F37:G37"/>
-    <mergeCell ref="A86:B88"/>
-    <mergeCell ref="E86:E88"/>
-    <mergeCell ref="F86:G88"/>
-    <mergeCell ref="H86:I88"/>
-    <mergeCell ref="J86:K88"/>
+    <mergeCell ref="F45:G45"/>
+    <mergeCell ref="H9:I10"/>
+    <mergeCell ref="J9:K10"/>
+    <mergeCell ref="F9:G10"/>
+    <mergeCell ref="A11:B12"/>
+    <mergeCell ref="A13:B14"/>
+    <mergeCell ref="A15:B16"/>
     <mergeCell ref="J11:K12"/>
     <mergeCell ref="J13:K14"/>
     <mergeCell ref="J15:K16"/>
@@ -5113,21 +5290,11 @@
     <mergeCell ref="F21:G22"/>
     <mergeCell ref="F23:G25"/>
     <mergeCell ref="H11:I12"/>
-    <mergeCell ref="A95:B98"/>
-    <mergeCell ref="E95:E98"/>
-    <mergeCell ref="F95:G98"/>
-    <mergeCell ref="H95:I98"/>
-    <mergeCell ref="J95:K98"/>
-    <mergeCell ref="A99:B100"/>
-    <mergeCell ref="E99:E100"/>
-    <mergeCell ref="F99:G100"/>
-    <mergeCell ref="H99:I100"/>
-    <mergeCell ref="J99:K100"/>
-    <mergeCell ref="J31:K34"/>
-    <mergeCell ref="H31:I34"/>
-    <mergeCell ref="F31:G34"/>
-    <mergeCell ref="E31:E34"/>
-    <mergeCell ref="A31:B34"/>
+    <mergeCell ref="H13:I14"/>
+    <mergeCell ref="H15:I16"/>
+    <mergeCell ref="H17:I18"/>
+    <mergeCell ref="H19:I20"/>
+    <mergeCell ref="H21:I22"/>
     <mergeCell ref="A30:K30"/>
     <mergeCell ref="A53:K53"/>
     <mergeCell ref="A80:B80"/>
@@ -5140,6 +5307,42 @@
     <mergeCell ref="F72:G74"/>
     <mergeCell ref="H72:I74"/>
     <mergeCell ref="J72:K74"/>
+    <mergeCell ref="J44:K44"/>
+    <mergeCell ref="J56:K56"/>
+    <mergeCell ref="J42:K42"/>
+    <mergeCell ref="J58:K58"/>
+    <mergeCell ref="J36:K36"/>
+    <mergeCell ref="A44:B44"/>
+    <mergeCell ref="J75:K75"/>
+    <mergeCell ref="H38:I38"/>
+    <mergeCell ref="F59:G59"/>
+    <mergeCell ref="A49:B49"/>
+    <mergeCell ref="J76:K76"/>
+    <mergeCell ref="A55:B55"/>
+    <mergeCell ref="F124:G124"/>
+    <mergeCell ref="J124:K124"/>
+    <mergeCell ref="H124:I124"/>
+    <mergeCell ref="A124:B124"/>
+    <mergeCell ref="J31:K34"/>
+    <mergeCell ref="H31:I34"/>
+    <mergeCell ref="F31:G34"/>
+    <mergeCell ref="E31:E34"/>
+    <mergeCell ref="A31:B34"/>
+    <mergeCell ref="J112:K112"/>
+    <mergeCell ref="A123:B123"/>
+    <mergeCell ref="J111:K111"/>
+    <mergeCell ref="F107:G107"/>
+    <mergeCell ref="H107:I107"/>
+    <mergeCell ref="F81:G81"/>
+    <mergeCell ref="H81:I81"/>
+    <mergeCell ref="J90:K90"/>
+    <mergeCell ref="A83:B83"/>
+    <mergeCell ref="A37:B37"/>
+    <mergeCell ref="A36:B36"/>
+    <mergeCell ref="A86:B88"/>
+    <mergeCell ref="E86:E88"/>
+    <mergeCell ref="F86:G88"/>
+    <mergeCell ref="H86:I88"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -5160,15 +5363,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1" s="76" t="s">
+      <c r="A1" s="90" t="s">
         <v>434</v>
       </c>
-      <c r="B1" s="73"/>
-      <c r="C1" s="73"/>
-      <c r="D1" s="73"/>
-      <c r="E1" s="73"/>
-      <c r="F1" s="73"/>
-      <c r="G1" s="73"/>
+      <c r="B1" s="85"/>
+      <c r="C1" s="85"/>
+      <c r="D1" s="85"/>
+      <c r="E1" s="85"/>
+      <c r="F1" s="85"/>
+      <c r="G1" s="85"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="7" t="s">
@@ -5194,7 +5397,7 @@
       </c>
     </row>
     <row r="3" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A3" s="75" t="s">
+      <c r="A3" s="89" t="s">
         <v>451</v>
       </c>
       <c r="B3" s="2">
@@ -5211,7 +5414,7 @@
       <c r="G3" s="3"/>
     </row>
     <row r="4" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A4" s="72"/>
+      <c r="A4" s="87"/>
       <c r="B4" s="2">
         <v>2</v>
       </c>
@@ -5226,7 +5429,7 @@
       <c r="G4" s="3"/>
     </row>
     <row r="5" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A5" s="72"/>
+      <c r="A5" s="87"/>
       <c r="B5" s="2">
         <v>3</v>
       </c>
@@ -5241,7 +5444,7 @@
       <c r="G5" s="3"/>
     </row>
     <row r="6" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A6" s="72"/>
+      <c r="A6" s="87"/>
       <c r="B6" s="2">
         <v>4</v>
       </c>
@@ -5256,7 +5459,7 @@
       <c r="G6" s="3"/>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A7" s="72"/>
+      <c r="A7" s="87"/>
       <c r="B7" s="2">
         <v>5</v>
       </c>
@@ -5271,7 +5474,7 @@
       <c r="G7" s="3"/>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A8" s="72"/>
+      <c r="A8" s="87"/>
       <c r="B8" s="2">
         <v>6</v>
       </c>
@@ -5286,7 +5489,7 @@
       <c r="G8" s="3"/>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A9" s="72"/>
+      <c r="A9" s="87"/>
       <c r="B9" s="2">
         <v>7</v>
       </c>
@@ -5323,15 +5526,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1" s="76" t="s">
+      <c r="A1" s="90" t="s">
         <v>434</v>
       </c>
-      <c r="B1" s="73"/>
-      <c r="C1" s="73"/>
-      <c r="D1" s="73"/>
-      <c r="E1" s="73"/>
-      <c r="F1" s="73"/>
-      <c r="G1" s="73"/>
+      <c r="B1" s="85"/>
+      <c r="C1" s="85"/>
+      <c r="D1" s="85"/>
+      <c r="E1" s="85"/>
+      <c r="F1" s="85"/>
+      <c r="G1" s="85"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="7" t="s">
@@ -5357,7 +5560,7 @@
       </c>
     </row>
     <row r="3" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A3" s="75" t="s">
+      <c r="A3" s="89" t="s">
         <v>466</v>
       </c>
       <c r="B3" s="2">
@@ -5374,7 +5577,7 @@
       <c r="G3" s="3"/>
     </row>
     <row r="4" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A4" s="72"/>
+      <c r="A4" s="87"/>
       <c r="B4" s="2">
         <v>2</v>
       </c>
@@ -5389,7 +5592,7 @@
       <c r="G4" s="3"/>
     </row>
     <row r="5" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A5" s="72"/>
+      <c r="A5" s="87"/>
       <c r="B5" s="2">
         <v>3</v>
       </c>
@@ -5404,7 +5607,7 @@
       <c r="G5" s="3"/>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A6" s="72"/>
+      <c r="A6" s="87"/>
       <c r="B6" s="2">
         <v>4</v>
       </c>
@@ -5419,7 +5622,7 @@
       <c r="G6" s="3"/>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A7" s="72"/>
+      <c r="A7" s="87"/>
       <c r="B7" s="2">
         <v>5</v>
       </c>
@@ -5434,7 +5637,7 @@
       <c r="G7" s="3"/>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A8" s="72"/>
+      <c r="A8" s="87"/>
       <c r="B8" s="2">
         <v>6</v>
       </c>
@@ -5449,7 +5652,7 @@
       <c r="G8" s="3"/>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A9" s="72"/>
+      <c r="A9" s="87"/>
       <c r="B9" s="2">
         <v>7</v>
       </c>
@@ -5486,15 +5689,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1" s="76" t="s">
+      <c r="A1" s="90" t="s">
         <v>479</v>
       </c>
-      <c r="B1" s="73"/>
-      <c r="C1" s="73"/>
-      <c r="D1" s="73"/>
-      <c r="E1" s="73"/>
-      <c r="F1" s="73"/>
-      <c r="G1" s="73"/>
+      <c r="B1" s="85"/>
+      <c r="C1" s="85"/>
+      <c r="D1" s="85"/>
+      <c r="E1" s="85"/>
+      <c r="F1" s="85"/>
+      <c r="G1" s="85"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="7" t="s">
@@ -5520,7 +5723,7 @@
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A3" s="75" t="s">
+      <c r="A3" s="89" t="s">
         <v>480</v>
       </c>
       <c r="B3" s="2">
@@ -5537,7 +5740,7 @@
       <c r="G3" s="3"/>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A4" s="72"/>
+      <c r="A4" s="87"/>
       <c r="B4" s="2">
         <v>2</v>
       </c>
@@ -5552,7 +5755,7 @@
       <c r="G4" s="3"/>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A5" s="72"/>
+      <c r="A5" s="87"/>
       <c r="B5" s="2">
         <v>3</v>
       </c>
@@ -5567,7 +5770,7 @@
       <c r="G5" s="3"/>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A6" s="72"/>
+      <c r="A6" s="87"/>
       <c r="B6" s="2">
         <v>4</v>
       </c>
@@ -5582,7 +5785,7 @@
       <c r="G6" s="3"/>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A7" s="72"/>
+      <c r="A7" s="87"/>
       <c r="B7" s="2">
         <v>5</v>
       </c>
@@ -5597,7 +5800,7 @@
       <c r="G7" s="3"/>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A8" s="72"/>
+      <c r="A8" s="87"/>
       <c r="B8" s="2">
         <v>6</v>
       </c>
@@ -5612,7 +5815,7 @@
       <c r="G8" s="3"/>
     </row>
     <row r="9" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A9" s="72"/>
+      <c r="A9" s="87"/>
       <c r="B9" s="2">
         <v>7</v>
       </c>
@@ -5627,7 +5830,7 @@
       <c r="G9" s="3"/>
     </row>
     <row r="10" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A10" s="72"/>
+      <c r="A10" s="87"/>
       <c r="B10" s="2">
         <v>8</v>
       </c>
@@ -5642,7 +5845,7 @@
       <c r="G10" s="3"/>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A11" s="72"/>
+      <c r="A11" s="87"/>
       <c r="B11" s="2">
         <v>9</v>
       </c>
@@ -5657,7 +5860,7 @@
       <c r="G11" s="3"/>
     </row>
     <row r="12" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A12" s="72"/>
+      <c r="A12" s="87"/>
       <c r="B12" s="2">
         <v>10</v>
       </c>
@@ -5694,15 +5897,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1" s="76" t="s">
+      <c r="A1" s="90" t="s">
         <v>434</v>
       </c>
-      <c r="B1" s="73"/>
-      <c r="C1" s="73"/>
-      <c r="D1" s="73"/>
-      <c r="E1" s="73"/>
-      <c r="F1" s="73"/>
-      <c r="G1" s="73"/>
+      <c r="B1" s="85"/>
+      <c r="C1" s="85"/>
+      <c r="D1" s="85"/>
+      <c r="E1" s="85"/>
+      <c r="F1" s="85"/>
+      <c r="G1" s="85"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="7" t="s">
@@ -5728,7 +5931,7 @@
       </c>
     </row>
     <row r="3" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A3" s="75" t="s">
+      <c r="A3" s="89" t="s">
         <v>496</v>
       </c>
       <c r="B3" s="2">
@@ -5745,7 +5948,7 @@
       <c r="G3" s="3"/>
     </row>
     <row r="4" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A4" s="72"/>
+      <c r="A4" s="87"/>
       <c r="B4" s="2">
         <v>2</v>
       </c>
@@ -5760,7 +5963,7 @@
       <c r="G4" s="3"/>
     </row>
     <row r="5" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A5" s="72"/>
+      <c r="A5" s="87"/>
       <c r="B5" s="2">
         <v>3</v>
       </c>
@@ -5775,7 +5978,7 @@
       <c r="G5" s="3"/>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A6" s="72"/>
+      <c r="A6" s="87"/>
       <c r="B6" s="2">
         <v>4</v>
       </c>
@@ -5790,7 +5993,7 @@
       <c r="G6" s="3"/>
     </row>
     <row r="7" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A7" s="72"/>
+      <c r="A7" s="87"/>
       <c r="B7" s="2">
         <v>5</v>
       </c>
@@ -5805,7 +6008,7 @@
       <c r="G7" s="3"/>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A8" s="72"/>
+      <c r="A8" s="87"/>
       <c r="B8" s="2">
         <v>6</v>
       </c>
@@ -5842,15 +6045,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1" s="76" t="s">
+      <c r="A1" s="90" t="s">
         <v>434</v>
       </c>
-      <c r="B1" s="73"/>
-      <c r="C1" s="73"/>
-      <c r="D1" s="73"/>
-      <c r="E1" s="73"/>
-      <c r="F1" s="73"/>
-      <c r="G1" s="73"/>
+      <c r="B1" s="85"/>
+      <c r="C1" s="85"/>
+      <c r="D1" s="85"/>
+      <c r="E1" s="85"/>
+      <c r="F1" s="85"/>
+      <c r="G1" s="85"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="7" t="s">
@@ -5876,7 +6079,7 @@
       </c>
     </row>
     <row r="3" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A3" s="75" t="s">
+      <c r="A3" s="89" t="s">
         <v>507</v>
       </c>
       <c r="B3" s="2">
@@ -5893,7 +6096,7 @@
       <c r="G3" s="3"/>
     </row>
     <row r="4" spans="1:7" ht="45" x14ac:dyDescent="0.25">
-      <c r="A4" s="72"/>
+      <c r="A4" s="87"/>
       <c r="B4" s="2">
         <v>2</v>
       </c>
@@ -5908,7 +6111,7 @@
       <c r="G4" s="3"/>
     </row>
     <row r="5" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A5" s="72"/>
+      <c r="A5" s="87"/>
       <c r="B5" s="2">
         <v>3</v>
       </c>
@@ -5937,173 +6140,173 @@
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="5" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A5" s="69" t="s">
+      <c r="A5" s="83" t="s">
         <v>272</v>
       </c>
-      <c r="B5" s="73"/>
-      <c r="C5" s="73"/>
-      <c r="D5" s="73"/>
-      <c r="E5" s="73"/>
-      <c r="F5" s="73"/>
-      <c r="G5" s="73"/>
-      <c r="H5" s="73"/>
-      <c r="I5" s="73"/>
-      <c r="J5" s="73"/>
-      <c r="K5" s="73"/>
+      <c r="B5" s="85"/>
+      <c r="C5" s="85"/>
+      <c r="D5" s="85"/>
+      <c r="E5" s="85"/>
+      <c r="F5" s="85"/>
+      <c r="G5" s="85"/>
+      <c r="H5" s="85"/>
+      <c r="I5" s="85"/>
+      <c r="J5" s="85"/>
+      <c r="K5" s="85"/>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A7" s="69" t="s">
+      <c r="A7" s="83" t="s">
         <v>273</v>
       </c>
-      <c r="B7" s="73"/>
-      <c r="C7" s="73"/>
-      <c r="D7" s="73"/>
-      <c r="E7" s="73"/>
-      <c r="F7" s="73"/>
-      <c r="G7" s="73"/>
-      <c r="H7" s="73"/>
-      <c r="I7" s="73"/>
-      <c r="J7" s="73"/>
-      <c r="K7" s="73"/>
+      <c r="B7" s="85"/>
+      <c r="C7" s="85"/>
+      <c r="D7" s="85"/>
+      <c r="E7" s="85"/>
+      <c r="F7" s="85"/>
+      <c r="G7" s="85"/>
+      <c r="H7" s="85"/>
+      <c r="I7" s="85"/>
+      <c r="J7" s="85"/>
+      <c r="K7" s="85"/>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A8" s="71" t="s">
+      <c r="A8" s="88" t="s">
         <v>274</v>
       </c>
-      <c r="B8" s="72"/>
-      <c r="C8" s="72"/>
-      <c r="D8" s="74" t="s">
+      <c r="B8" s="87"/>
+      <c r="C8" s="87"/>
+      <c r="D8" s="86" t="s">
         <v>275</v>
       </c>
-      <c r="E8" s="72"/>
-      <c r="F8" s="72"/>
-      <c r="G8" s="72"/>
-      <c r="H8" s="72"/>
-      <c r="I8" s="72"/>
-      <c r="J8" s="72"/>
-      <c r="K8" s="72"/>
+      <c r="E8" s="87"/>
+      <c r="F8" s="87"/>
+      <c r="G8" s="87"/>
+      <c r="H8" s="87"/>
+      <c r="I8" s="87"/>
+      <c r="J8" s="87"/>
+      <c r="K8" s="87"/>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A9" s="71" t="s">
+      <c r="A9" s="88" t="s">
         <v>276</v>
       </c>
-      <c r="B9" s="72"/>
-      <c r="C9" s="72"/>
-      <c r="D9" s="74"/>
-      <c r="E9" s="72"/>
-      <c r="F9" s="72"/>
-      <c r="G9" s="72"/>
-      <c r="H9" s="72"/>
-      <c r="I9" s="72"/>
-      <c r="J9" s="72"/>
-      <c r="K9" s="72"/>
+      <c r="B9" s="87"/>
+      <c r="C9" s="87"/>
+      <c r="D9" s="86"/>
+      <c r="E9" s="87"/>
+      <c r="F9" s="87"/>
+      <c r="G9" s="87"/>
+      <c r="H9" s="87"/>
+      <c r="I9" s="87"/>
+      <c r="J9" s="87"/>
+      <c r="K9" s="87"/>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A10" s="71" t="s">
+      <c r="A10" s="88" t="s">
         <v>277</v>
       </c>
-      <c r="B10" s="72"/>
-      <c r="C10" s="72"/>
-      <c r="D10" s="74" t="s">
+      <c r="B10" s="87"/>
+      <c r="C10" s="87"/>
+      <c r="D10" s="86" t="s">
         <v>278</v>
       </c>
-      <c r="E10" s="72"/>
-      <c r="F10" s="72"/>
-      <c r="G10" s="72"/>
-      <c r="H10" s="72"/>
-      <c r="I10" s="72"/>
-      <c r="J10" s="72"/>
-      <c r="K10" s="72"/>
+      <c r="E10" s="87"/>
+      <c r="F10" s="87"/>
+      <c r="G10" s="87"/>
+      <c r="H10" s="87"/>
+      <c r="I10" s="87"/>
+      <c r="J10" s="87"/>
+      <c r="K10" s="87"/>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A11" s="71" t="s">
+      <c r="A11" s="88" t="s">
         <v>279</v>
       </c>
-      <c r="B11" s="72"/>
-      <c r="C11" s="72"/>
-      <c r="D11" s="74" t="s">
+      <c r="B11" s="87"/>
+      <c r="C11" s="87"/>
+      <c r="D11" s="86" t="s">
         <v>280</v>
       </c>
-      <c r="E11" s="72"/>
-      <c r="F11" s="72"/>
-      <c r="G11" s="72"/>
-      <c r="H11" s="72"/>
-      <c r="I11" s="72"/>
-      <c r="J11" s="72"/>
-      <c r="K11" s="72"/>
+      <c r="E11" s="87"/>
+      <c r="F11" s="87"/>
+      <c r="G11" s="87"/>
+      <c r="H11" s="87"/>
+      <c r="I11" s="87"/>
+      <c r="J11" s="87"/>
+      <c r="K11" s="87"/>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A12" s="71" t="s">
+      <c r="A12" s="88" t="s">
         <v>281</v>
       </c>
-      <c r="B12" s="72"/>
-      <c r="C12" s="72"/>
-      <c r="D12" s="74"/>
-      <c r="E12" s="72"/>
-      <c r="F12" s="72"/>
-      <c r="G12" s="72"/>
-      <c r="H12" s="72"/>
-      <c r="I12" s="72"/>
-      <c r="J12" s="72"/>
-      <c r="K12" s="72"/>
+      <c r="B12" s="87"/>
+      <c r="C12" s="87"/>
+      <c r="D12" s="86"/>
+      <c r="E12" s="87"/>
+      <c r="F12" s="87"/>
+      <c r="G12" s="87"/>
+      <c r="H12" s="87"/>
+      <c r="I12" s="87"/>
+      <c r="J12" s="87"/>
+      <c r="K12" s="87"/>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A13" s="71"/>
-      <c r="B13" s="72"/>
-      <c r="C13" s="72"/>
-      <c r="D13" s="74"/>
-      <c r="E13" s="72"/>
-      <c r="F13" s="72"/>
-      <c r="G13" s="72"/>
-      <c r="H13" s="72"/>
-      <c r="I13" s="72"/>
-      <c r="J13" s="72"/>
-      <c r="K13" s="72"/>
+      <c r="A13" s="88"/>
+      <c r="B13" s="87"/>
+      <c r="C13" s="87"/>
+      <c r="D13" s="86"/>
+      <c r="E13" s="87"/>
+      <c r="F13" s="87"/>
+      <c r="G13" s="87"/>
+      <c r="H13" s="87"/>
+      <c r="I13" s="87"/>
+      <c r="J13" s="87"/>
+      <c r="K13" s="87"/>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A14" s="71" t="s">
+      <c r="A14" s="88" t="s">
         <v>282</v>
       </c>
-      <c r="B14" s="72"/>
-      <c r="C14" s="72"/>
-      <c r="D14" s="74"/>
-      <c r="E14" s="72"/>
-      <c r="F14" s="72"/>
-      <c r="G14" s="72"/>
-      <c r="H14" s="72"/>
-      <c r="I14" s="72"/>
-      <c r="J14" s="72"/>
-      <c r="K14" s="72"/>
+      <c r="B14" s="87"/>
+      <c r="C14" s="87"/>
+      <c r="D14" s="86"/>
+      <c r="E14" s="87"/>
+      <c r="F14" s="87"/>
+      <c r="G14" s="87"/>
+      <c r="H14" s="87"/>
+      <c r="I14" s="87"/>
+      <c r="J14" s="87"/>
+      <c r="K14" s="87"/>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A15" s="71" t="s">
+      <c r="A15" s="88" t="s">
         <v>283</v>
       </c>
-      <c r="B15" s="72"/>
-      <c r="C15" s="72"/>
-      <c r="D15" s="74"/>
-      <c r="E15" s="72"/>
-      <c r="F15" s="72"/>
-      <c r="G15" s="72"/>
-      <c r="H15" s="72"/>
-      <c r="I15" s="72"/>
-      <c r="J15" s="72"/>
-      <c r="K15" s="72"/>
+      <c r="B15" s="87"/>
+      <c r="C15" s="87"/>
+      <c r="D15" s="86"/>
+      <c r="E15" s="87"/>
+      <c r="F15" s="87"/>
+      <c r="G15" s="87"/>
+      <c r="H15" s="87"/>
+      <c r="I15" s="87"/>
+      <c r="J15" s="87"/>
+      <c r="K15" s="87"/>
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A17" s="69" t="s">
+      <c r="A17" s="83" t="s">
         <v>284</v>
       </c>
-      <c r="B17" s="73"/>
-      <c r="C17" s="73"/>
-      <c r="D17" s="73"/>
-      <c r="E17" s="73"/>
-      <c r="F17" s="73"/>
-      <c r="G17" s="73"/>
-      <c r="H17" s="73"/>
-      <c r="I17" s="73"/>
-      <c r="J17" s="73"/>
-      <c r="K17" s="73"/>
+      <c r="B17" s="85"/>
+      <c r="C17" s="85"/>
+      <c r="D17" s="85"/>
+      <c r="E17" s="85"/>
+      <c r="F17" s="85"/>
+      <c r="G17" s="85"/>
+      <c r="H17" s="85"/>
+      <c r="I17" s="85"/>
+      <c r="J17" s="85"/>
+      <c r="K17" s="85"/>
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A19" s="6" t="s">
@@ -6188,7 +6391,6 @@
     </row>
   </sheetData>
   <mergeCells count="19">
-    <mergeCell ref="A8:C8"/>
     <mergeCell ref="A7:K7"/>
     <mergeCell ref="D11:K11"/>
     <mergeCell ref="A15:C15"/>
@@ -6207,6 +6409,7 @@
     <mergeCell ref="A9:C9"/>
     <mergeCell ref="D10:K10"/>
     <mergeCell ref="A12:C12"/>
+    <mergeCell ref="A8:C8"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -6518,15 +6721,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1" s="76" t="s">
+      <c r="A1" s="90" t="s">
         <v>339</v>
       </c>
-      <c r="B1" s="73"/>
-      <c r="C1" s="73"/>
-      <c r="D1" s="73"/>
-      <c r="E1" s="73"/>
-      <c r="F1" s="73"/>
-      <c r="G1" s="73"/>
+      <c r="B1" s="85"/>
+      <c r="C1" s="85"/>
+      <c r="D1" s="85"/>
+      <c r="E1" s="85"/>
+      <c r="F1" s="85"/>
+      <c r="G1" s="85"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="7" t="s">
@@ -6552,7 +6755,7 @@
       </c>
     </row>
     <row r="3" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A3" s="75" t="s">
+      <c r="A3" s="89" t="s">
         <v>344</v>
       </c>
       <c r="B3" s="2">
@@ -6569,7 +6772,7 @@
       <c r="G3" s="3"/>
     </row>
     <row r="4" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A4" s="72"/>
+      <c r="A4" s="87"/>
       <c r="B4" s="2">
         <v>2</v>
       </c>
@@ -6584,7 +6787,7 @@
       <c r="G4" s="3"/>
     </row>
     <row r="5" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A5" s="72"/>
+      <c r="A5" s="87"/>
       <c r="B5" s="2">
         <v>3</v>
       </c>
@@ -6599,7 +6802,7 @@
       <c r="G5" s="3"/>
     </row>
     <row r="6" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A6" s="72"/>
+      <c r="A6" s="87"/>
       <c r="B6" s="2">
         <v>4</v>
       </c>
@@ -6614,7 +6817,7 @@
       <c r="G6" s="3"/>
     </row>
     <row r="7" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A7" s="72"/>
+      <c r="A7" s="87"/>
       <c r="B7" s="2">
         <v>5</v>
       </c>
@@ -6629,7 +6832,7 @@
       <c r="G7" s="3"/>
     </row>
     <row r="8" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A8" s="72"/>
+      <c r="A8" s="87"/>
       <c r="B8" s="2">
         <v>6</v>
       </c>
@@ -6644,7 +6847,7 @@
       <c r="G8" s="3"/>
     </row>
     <row r="9" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A9" s="72"/>
+      <c r="A9" s="87"/>
       <c r="B9" s="2">
         <v>7</v>
       </c>
@@ -6659,7 +6862,7 @@
       <c r="G9" s="3"/>
     </row>
     <row r="10" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A10" s="72"/>
+      <c r="A10" s="87"/>
       <c r="B10" s="2">
         <v>8</v>
       </c>
@@ -6674,7 +6877,7 @@
       <c r="G10" s="3"/>
     </row>
     <row r="11" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A11" s="72"/>
+      <c r="A11" s="87"/>
       <c r="B11" s="2">
         <v>9</v>
       </c>
@@ -6689,7 +6892,7 @@
       <c r="G11" s="3"/>
     </row>
     <row r="12" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A12" s="72"/>
+      <c r="A12" s="87"/>
       <c r="B12" s="2">
         <v>10</v>
       </c>
@@ -6726,15 +6929,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1" s="76" t="s">
+      <c r="A1" s="90" t="s">
         <v>362</v>
       </c>
-      <c r="B1" s="73"/>
-      <c r="C1" s="73"/>
-      <c r="D1" s="73"/>
-      <c r="E1" s="73"/>
-      <c r="F1" s="73"/>
-      <c r="G1" s="73"/>
+      <c r="B1" s="85"/>
+      <c r="C1" s="85"/>
+      <c r="D1" s="85"/>
+      <c r="E1" s="85"/>
+      <c r="F1" s="85"/>
+      <c r="G1" s="85"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="7" t="s">
@@ -6760,7 +6963,7 @@
       </c>
     </row>
     <row r="3" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A3" s="75" t="s">
+      <c r="A3" s="89" t="s">
         <v>363</v>
       </c>
       <c r="B3" s="2">
@@ -6777,7 +6980,7 @@
       <c r="G3" s="3"/>
     </row>
     <row r="4" spans="1:7" ht="45" x14ac:dyDescent="0.25">
-      <c r="A4" s="72"/>
+      <c r="A4" s="87"/>
       <c r="B4" s="2">
         <v>2</v>
       </c>
@@ -6792,7 +6995,7 @@
       <c r="G4" s="3"/>
     </row>
     <row r="5" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A5" s="72"/>
+      <c r="A5" s="87"/>
       <c r="B5" s="2">
         <v>3</v>
       </c>
@@ -6807,7 +7010,7 @@
       <c r="G5" s="3"/>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A6" s="72"/>
+      <c r="A6" s="87"/>
       <c r="B6" s="2">
         <v>4</v>
       </c>
@@ -6822,7 +7025,7 @@
       <c r="G6" s="3"/>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A7" s="72"/>
+      <c r="A7" s="87"/>
       <c r="B7" s="2">
         <v>5</v>
       </c>
@@ -6837,7 +7040,7 @@
       <c r="G7" s="3"/>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A8" s="72"/>
+      <c r="A8" s="87"/>
       <c r="B8" s="2">
         <v>6</v>
       </c>
@@ -6852,7 +7055,7 @@
       <c r="G8" s="3"/>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A9" s="72"/>
+      <c r="A9" s="87"/>
       <c r="B9" s="2">
         <v>7</v>
       </c>
@@ -6867,7 +7070,7 @@
       <c r="G9" s="3"/>
     </row>
     <row r="10" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A10" s="72"/>
+      <c r="A10" s="87"/>
       <c r="B10" s="2">
         <v>8</v>
       </c>
@@ -6882,7 +7085,7 @@
       <c r="G10" s="3"/>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A11" s="72"/>
+      <c r="A11" s="87"/>
       <c r="B11" s="2">
         <v>9</v>
       </c>
@@ -6897,7 +7100,7 @@
       <c r="G11" s="3"/>
     </row>
     <row r="12" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A12" s="72"/>
+      <c r="A12" s="87"/>
       <c r="B12" s="2">
         <v>10</v>
       </c>
@@ -6912,7 +7115,7 @@
       <c r="G12" s="3"/>
     </row>
     <row r="13" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A13" s="72"/>
+      <c r="A13" s="87"/>
       <c r="B13" s="2">
         <v>11</v>
       </c>
@@ -6927,7 +7130,7 @@
       <c r="G13" s="3"/>
     </row>
     <row r="14" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A14" s="72"/>
+      <c r="A14" s="87"/>
       <c r="B14" s="2">
         <v>12</v>
       </c>
@@ -6942,7 +7145,7 @@
       <c r="G14" s="3"/>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A15" s="72"/>
+      <c r="A15" s="87"/>
       <c r="B15" s="2">
         <v>13</v>
       </c>
@@ -6957,7 +7160,7 @@
       <c r="G15" s="3"/>
     </row>
     <row r="16" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A16" s="72"/>
+      <c r="A16" s="87"/>
       <c r="B16" s="2">
         <v>14</v>
       </c>
@@ -6972,7 +7175,7 @@
       <c r="G16" s="3"/>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A17" s="72"/>
+      <c r="A17" s="87"/>
       <c r="B17" s="2">
         <v>15</v>
       </c>
@@ -6987,7 +7190,7 @@
       <c r="G17" s="3"/>
     </row>
     <row r="18" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A18" s="72"/>
+      <c r="A18" s="87"/>
       <c r="B18" s="2">
         <v>16</v>
       </c>
@@ -7002,7 +7205,7 @@
       <c r="G18" s="3"/>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A19" s="72"/>
+      <c r="A19" s="87"/>
       <c r="B19" s="2">
         <v>17</v>
       </c>
@@ -7039,15 +7242,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1" s="76" t="s">
+      <c r="A1" s="90" t="s">
         <v>396</v>
       </c>
-      <c r="B1" s="73"/>
-      <c r="C1" s="73"/>
-      <c r="D1" s="73"/>
-      <c r="E1" s="73"/>
-      <c r="F1" s="73"/>
-      <c r="G1" s="73"/>
+      <c r="B1" s="85"/>
+      <c r="C1" s="85"/>
+      <c r="D1" s="85"/>
+      <c r="E1" s="85"/>
+      <c r="F1" s="85"/>
+      <c r="G1" s="85"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="7" t="s">
@@ -7073,7 +7276,7 @@
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A3" s="75" t="s">
+      <c r="A3" s="89" t="s">
         <v>397</v>
       </c>
       <c r="B3" s="2">
@@ -7090,7 +7293,7 @@
       <c r="G3" s="3"/>
     </row>
     <row r="4" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A4" s="72"/>
+      <c r="A4" s="87"/>
       <c r="B4" s="2">
         <v>2</v>
       </c>
@@ -7105,7 +7308,7 @@
       <c r="G4" s="3"/>
     </row>
     <row r="5" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A5" s="72"/>
+      <c r="A5" s="87"/>
       <c r="B5" s="2">
         <v>3</v>
       </c>
@@ -7120,7 +7323,7 @@
       <c r="G5" s="3"/>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A6" s="72"/>
+      <c r="A6" s="87"/>
       <c r="B6" s="2">
         <v>4</v>
       </c>
@@ -7135,7 +7338,7 @@
       <c r="G6" s="3"/>
     </row>
     <row r="7" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A7" s="72"/>
+      <c r="A7" s="87"/>
       <c r="B7" s="2">
         <v>5</v>
       </c>
@@ -7150,7 +7353,7 @@
       <c r="G7" s="3"/>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A8" s="72"/>
+      <c r="A8" s="87"/>
       <c r="B8" s="2">
         <v>6</v>
       </c>
@@ -7165,7 +7368,7 @@
       <c r="G8" s="3"/>
     </row>
     <row r="9" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A9" s="72"/>
+      <c r="A9" s="87"/>
       <c r="B9" s="2">
         <v>7</v>
       </c>
@@ -7180,7 +7383,7 @@
       <c r="G9" s="3"/>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A10" s="72"/>
+      <c r="A10" s="87"/>
       <c r="B10" s="2">
         <v>8</v>
       </c>
@@ -7195,7 +7398,7 @@
       <c r="G10" s="3"/>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A11" s="72"/>
+      <c r="A11" s="87"/>
       <c r="B11" s="2">
         <v>9</v>
       </c>
@@ -7210,7 +7413,7 @@
       <c r="G11" s="3"/>
     </row>
     <row r="12" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A12" s="72"/>
+      <c r="A12" s="87"/>
       <c r="B12" s="2">
         <v>10</v>
       </c>
@@ -7225,7 +7428,7 @@
       <c r="G12" s="3"/>
     </row>
     <row r="13" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A13" s="72"/>
+      <c r="A13" s="87"/>
       <c r="B13" s="2">
         <v>11</v>
       </c>
@@ -7262,15 +7465,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1" s="76" t="s">
+      <c r="A1" s="90" t="s">
         <v>339</v>
       </c>
-      <c r="B1" s="73"/>
-      <c r="C1" s="73"/>
-      <c r="D1" s="73"/>
-      <c r="E1" s="73"/>
-      <c r="F1" s="73"/>
-      <c r="G1" s="73"/>
+      <c r="B1" s="85"/>
+      <c r="C1" s="85"/>
+      <c r="D1" s="85"/>
+      <c r="E1" s="85"/>
+      <c r="F1" s="85"/>
+      <c r="G1" s="85"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="7" t="s">
@@ -7296,7 +7499,7 @@
       </c>
     </row>
     <row r="3" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A3" s="75" t="s">
+      <c r="A3" s="89" t="s">
         <v>418</v>
       </c>
       <c r="B3" s="2">
@@ -7313,7 +7516,7 @@
       <c r="G3" s="3"/>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A4" s="72"/>
+      <c r="A4" s="87"/>
       <c r="B4" s="2">
         <v>2</v>
       </c>
@@ -7328,7 +7531,7 @@
       <c r="G4" s="3"/>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A5" s="72"/>
+      <c r="A5" s="87"/>
       <c r="B5" s="2">
         <v>3</v>
       </c>
@@ -7343,7 +7546,7 @@
       <c r="G5" s="3"/>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A6" s="72"/>
+      <c r="A6" s="87"/>
       <c r="B6" s="2">
         <v>4</v>
       </c>
@@ -7358,7 +7561,7 @@
       <c r="G6" s="3"/>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A7" s="72"/>
+      <c r="A7" s="87"/>
       <c r="B7" s="2">
         <v>5</v>
       </c>
@@ -7373,7 +7576,7 @@
       <c r="G7" s="3"/>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A8" s="72"/>
+      <c r="A8" s="87"/>
       <c r="B8" s="2">
         <v>6</v>
       </c>
@@ -7388,7 +7591,7 @@
       <c r="G8" s="3"/>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A9" s="72"/>
+      <c r="A9" s="87"/>
       <c r="B9" s="2">
         <v>7</v>
       </c>
@@ -7403,7 +7606,7 @@
       <c r="G9" s="3"/>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A10" s="72"/>
+      <c r="A10" s="87"/>
       <c r="B10" s="2">
         <v>8</v>
       </c>
@@ -7440,15 +7643,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1" s="76" t="s">
+      <c r="A1" s="90" t="s">
         <v>434</v>
       </c>
-      <c r="B1" s="73"/>
-      <c r="C1" s="73"/>
-      <c r="D1" s="73"/>
-      <c r="E1" s="73"/>
-      <c r="F1" s="73"/>
-      <c r="G1" s="73"/>
+      <c r="B1" s="85"/>
+      <c r="C1" s="85"/>
+      <c r="D1" s="85"/>
+      <c r="E1" s="85"/>
+      <c r="F1" s="85"/>
+      <c r="G1" s="85"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="7" t="s">
@@ -7474,7 +7677,7 @@
       </c>
     </row>
     <row r="3" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A3" s="75" t="s">
+      <c r="A3" s="89" t="s">
         <v>435</v>
       </c>
       <c r="B3" s="2">
@@ -7491,7 +7694,7 @@
       <c r="G3" s="3"/>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A4" s="72"/>
+      <c r="A4" s="87"/>
       <c r="B4" s="2">
         <v>2</v>
       </c>
@@ -7506,7 +7709,7 @@
       <c r="G4" s="3"/>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A5" s="72"/>
+      <c r="A5" s="87"/>
       <c r="B5" s="2">
         <v>3</v>
       </c>
@@ -7521,7 +7724,7 @@
       <c r="G5" s="3"/>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A6" s="72"/>
+      <c r="A6" s="87"/>
       <c r="B6" s="2">
         <v>4</v>
       </c>
@@ -7536,7 +7739,7 @@
       <c r="G6" s="3"/>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A7" s="72"/>
+      <c r="A7" s="87"/>
       <c r="B7" s="2">
         <v>5</v>
       </c>
@@ -7551,7 +7754,7 @@
       <c r="G7" s="3"/>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A8" s="72"/>
+      <c r="A8" s="87"/>
       <c r="B8" s="2">
         <v>6</v>
       </c>
@@ -7566,7 +7769,7 @@
       <c r="G8" s="3"/>
     </row>
     <row r="9" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A9" s="72"/>
+      <c r="A9" s="87"/>
       <c r="B9" s="2">
         <v>7</v>
       </c>
@@ -7581,7 +7784,7 @@
       <c r="G9" s="3"/>
     </row>
     <row r="10" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A10" s="72"/>
+      <c r="A10" s="87"/>
       <c r="B10" s="2">
         <v>8</v>
       </c>
